--- a/Avantis Mapping/SPARQL_tag.xlsx
+++ b/Avantis Mapping/SPARQL_tag.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49761C1B-61EF-429E-8DF8-24DA37556D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1DCE2D0-20A4-49E4-8C35-6663796E11B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="224">
   <si>
     <t>TWONTO</t>
   </si>
@@ -53,9 +53,6 @@
     <t>GB</t>
   </si>
   <si>
-    <t>ALR</t>
-  </si>
-  <si>
     <t>CLR</t>
   </si>
   <si>
@@ -80,12 +77,6 @@
     <t>CU</t>
   </si>
   <si>
-    <t>PDM</t>
-  </si>
-  <si>
-    <t>CRN</t>
-  </si>
-  <si>
     <t>ENG</t>
   </si>
   <si>
@@ -110,18 +101,12 @@
     <t>ELV</t>
   </si>
   <si>
-    <t>SCBA</t>
-  </si>
-  <si>
     <t>LS</t>
   </si>
   <si>
     <t>PWU</t>
   </si>
   <si>
-    <t>MH</t>
-  </si>
-  <si>
     <t>DD</t>
   </si>
   <si>
@@ -140,21 +125,12 @@
     <t>FE</t>
   </si>
   <si>
-    <t>CBL</t>
-  </si>
-  <si>
     <t>AM</t>
   </si>
   <si>
-    <t>DIT</t>
-  </si>
-  <si>
     <t>STR</t>
   </si>
   <si>
-    <t>HF</t>
-  </si>
-  <si>
     <t>SB</t>
   </si>
   <si>
@@ -164,9 +140,6 @@
     <t>AC</t>
   </si>
   <si>
-    <t>LP</t>
-  </si>
-  <si>
     <t>HE</t>
   </si>
   <si>
@@ -179,9 +152,6 @@
     <t>AIT</t>
   </si>
   <si>
-    <t>TE</t>
-  </si>
-  <si>
     <t>INJ</t>
   </si>
   <si>
@@ -230,33 +200,15 @@
     <t>BU</t>
   </si>
   <si>
-    <t>DS</t>
-  </si>
-  <si>
     <t>FS</t>
   </si>
   <si>
     <t>HTR</t>
   </si>
   <si>
-    <t>GEN</t>
-  </si>
-  <si>
-    <t>WEL</t>
-  </si>
-  <si>
     <t>CM</t>
   </si>
   <si>
-    <t>CAP</t>
-  </si>
-  <si>
-    <t>LE</t>
-  </si>
-  <si>
-    <t>CMP</t>
-  </si>
-  <si>
     <t>CT</t>
   </si>
   <si>
@@ -272,12 +224,6 @@
     <t>QUEN</t>
   </si>
   <si>
-    <t>AFR</t>
-  </si>
-  <si>
-    <t>CP</t>
-  </si>
-  <si>
     <t>TS</t>
   </si>
   <si>
@@ -305,15 +251,6 @@
     <t>DM</t>
   </si>
   <si>
-    <t>ST</t>
-  </si>
-  <si>
-    <t>SPL</t>
-  </si>
-  <si>
-    <t>XSH</t>
-  </si>
-  <si>
     <t>BO</t>
   </si>
   <si>
@@ -341,9 +278,6 @@
     <t>FA</t>
   </si>
   <si>
-    <t>FAK</t>
-  </si>
-  <si>
     <t>LDR</t>
   </si>
   <si>
@@ -357,9 +291,6 @@
   </si>
   <si>
     <t>Tag</t>
-  </si>
-  <si>
-    <t>RTU</t>
   </si>
   <si>
     <t>PREFIX rdf: &lt;http://www.w3.org/1999/02/22-rdf-syntax-ns#&gt;
@@ -383,412 +314,409 @@
     <t>FCV</t>
   </si>
   <si>
-    <t>BL</t>
-  </si>
-  <si>
-    <t>WRT</t>
-  </si>
-  <si>
     <t>FT</t>
   </si>
   <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>FIT</t>
+  </si>
+  <si>
+    <t>PIT</t>
+  </si>
+  <si>
+    <t>LRT</t>
+  </si>
+  <si>
+    <t>LIT</t>
+  </si>
+  <si>
+    <t>ZT</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>ZIT</t>
+  </si>
+  <si>
+    <t>ZRT</t>
+  </si>
+  <si>
+    <t>FN</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#AC_evaporator_unit</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#instrument_sensor_element</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#chlorinator_system</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#ozone_generator</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#gearbox</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#pressure_transmitter</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#clarifier</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#pressurized_sewer_segment</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#channel_gate</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#security_camera</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#dehumidifier</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#engine</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#pipe_segment</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#chiller</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#centrifuge</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#air_handler_unit</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#auto_sampler</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#automatic_external_defibrillator</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#operator_interface_terminal</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#valve</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#elevator</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#level_switch</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#power_washer</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#display_panel</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#level_transmitter</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#roll_up_door</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#UV_disinfection_assembly</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#instrument_gauge_or_display</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#transformer</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#flow_element</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#fixed_gas_detector</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#strainer</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#air_scrubber</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#grinder_or_comminutor</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#air_condition</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#heat_exchanger</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#computer</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#AC_condenser_unit</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#instrument_transmitter</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#ejector</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#condensate_trap</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#classifier</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#flame_arrestor</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#outfall_or_discharge_point</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#air_duct_segment</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#hydrant</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#dust_collector</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#fire_rated_door</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#screen</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#mixer_or_agitator</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#UPS</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#furnace</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#reservoir_tank</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#variable_air_volume_unit</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#burner_component_of_asset</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#flow_switch</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#flowmeter</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#heater</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#collector_mechanism</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#controller</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#material_distribution_panel</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#controlled_door_access</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#flow_transmitter</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#server_appliance</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#motor</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#quencher</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#transfer_switch</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#reactor</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#trap_priming_device</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#battery</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#ash_lagoon</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#storage_tank</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#welding_receptacle</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#vibration_analyzer</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#compressor</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#air_damper</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#boiler</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#conveyor</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#equipment_or_access_chamber</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#hydraulic_power_pack</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#large_stationary_tool</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#surge_suppressor</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#backflow_preventer</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#annunciator_panel</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#ladder</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#data_logger</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#ground_and_test_device</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#humidifier</t>
+  </si>
+  <si>
+    <t>LSHH</t>
+  </si>
+  <si>
+    <t>LSLL</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#pressure_switch</t>
+  </si>
+  <si>
+    <t>PSH</t>
+  </si>
+  <si>
+    <t>LSL</t>
+  </si>
+  <si>
+    <t>LI</t>
+  </si>
+  <si>
+    <t>PSL</t>
+  </si>
+  <si>
+    <t>LSH</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#temperature_transmitter</t>
+  </si>
+  <si>
+    <t>TIT</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#position_sensing</t>
+  </si>
+  <si>
+    <t>PI</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#blower_or_fan_with_drive</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#MV_electrical_cabinet</t>
+  </si>
+  <si>
+    <t>BUS</t>
+  </si>
+  <si>
+    <t>TI</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#temperature_switch</t>
+  </si>
+  <si>
+    <t>TSH</t>
+  </si>
+  <si>
+    <t>FQ</t>
+  </si>
+  <si>
+    <t>TSL</t>
+  </si>
+  <si>
+    <t>TT</t>
+  </si>
+  <si>
+    <t>PSLL</t>
+  </si>
+  <si>
+    <t>PSHH</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#process_control_panel</t>
+  </si>
+  <si>
+    <t>CP</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#RPU_panel</t>
+  </si>
+  <si>
+    <t>RPU</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#cable_segment</t>
+  </si>
+  <si>
+    <t>CBL</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#position_switch</t>
+  </si>
+  <si>
+    <t>ZSH</t>
+  </si>
+  <si>
+    <t>ZSL</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#weight_scale</t>
+  </si>
+  <si>
+    <t>WSC</t>
+  </si>
+  <si>
     <t>WIT</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>FIT</t>
-  </si>
-  <si>
-    <t>PIT</t>
-  </si>
-  <si>
-    <t>WSC</t>
-  </si>
-  <si>
-    <t>LRT</t>
-  </si>
-  <si>
-    <t>LIT</t>
-  </si>
-  <si>
-    <t>ZT</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>ZIT</t>
-  </si>
-  <si>
-    <t>AMP</t>
-  </si>
-  <si>
-    <t>ZRT</t>
-  </si>
-  <si>
-    <t>FN</t>
-  </si>
-  <si>
-    <t>PA</t>
-  </si>
-  <si>
-    <t>RPU</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#AC_evaporator_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#RTU_panel</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_sensor_element</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#chlorinator_system</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#ozone_generator</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#gearbox</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pressure_transmitter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#alarm_device</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#clarifier</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#position_sensing_instrument</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pressurized_sewer_segment</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#weight_scale</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#channel_gate</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#security_camera</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#dehumidifier</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pulsation_dampener</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#crane</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#engine</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pipe_segment</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#chiller</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#centrifuge</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_handler_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#auto_sampler</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#motion_sensor_element</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#automatic_external_defibrillator</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#operator_interface_terminal</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#valve</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#elevator</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#self-contained_breathing_apparatus</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#level_switch</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#power_washer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#manhole</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#display_panel</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#level_transmitter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#roll_up_door</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#UV_disinfection_assembly</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_gauge_or_display</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#transformer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#flow_element</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#cable_segment</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#fixed_gas_detector</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#slude_density_meter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#strainer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#power_harmonic_filter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_scrubber</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#grinder_or_comminutor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_condition</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#heat_exchanger</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#computer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#AC_condenser_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_transmitter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#temperature_sensor_element</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#ejector</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#condensate_trap</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#classifier</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#flame_arrestor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#LV_electrical_panel</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#outfall_or_discharge_point</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_duct_segment</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#hydrant</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#dust_collector</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#fire_rated_door</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#screen</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#battery_charger</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#mixer_or_agitator</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#UPS</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#public_annoucement_speaker</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#furnace</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#reservoir_tank</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#variable_air_volume_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#burner_component_of_asset</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#disconnect_switch</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#flow_switch</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#flowmeter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#blower</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#heater</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#generator-set</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#well</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#collector_mechanism</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#capacitor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#level_sensor_element</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#compactor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#controller</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#material_distribution_panel</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#controlled_door_access</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#flow_transmitter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#server_appliance</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#motor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#quencher</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#protection_relay</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#process_control_panel</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#transfer_switch</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#reactor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#trap_priming_device</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#battery</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#ash_lagoon</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#storage_tank</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#welding_receptacle</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#vibration_analyzer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#compressor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_damper</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#motor_starter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#spill_kit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#torque_switch</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#boiler</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#conveyor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#equipment_or_access_chamber</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#hydraulic_power_pack</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#large_stationary_tool</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#surge_suppressor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#backflow_preventer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#annunciator_panel</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#first_aid_kit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#ladder</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#data_logger</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#ground_and_test_device</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#humidifier</t>
   </si>
 </sst>
 </file>
@@ -901,8 +829,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}" name="Table1" displayName="Table1" ref="A2:B135" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B135" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}" name="Table1" displayName="Table1" ref="A2:B128" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B128" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{6954C25C-9295-466B-8916-09F7AE9B1E9C}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{C2EFA1BF-9094-4221-B7A9-7713F0DEA95D}" name="Tag"/>
@@ -912,9 +840,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -952,7 +880,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1058,7 +986,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1200,7 +1128,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1208,7 +1136,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B135"/>
+  <dimension ref="A1:B128"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56.7109375" bestFit="1" customWidth="1"/>
@@ -1217,7 +1145,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="165" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1225,60 +1153,60 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>107</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="B6" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="B9" t="s">
         <v>5</v>
@@ -1286,23 +1214,23 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="B11" t="s">
-        <v>122</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="B12" t="s">
         <v>8</v>
@@ -1310,986 +1238,930 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>141</v>
+        <v>190</v>
       </c>
       <c r="B13" t="s">
-        <v>113</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>130</v>
+        <v>190</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="B17" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>146</v>
+        <v>100</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="B20" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>141</v>
+        <v>196</v>
       </c>
       <c r="B21" t="s">
-        <v>115</v>
+        <v>197</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="B22" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>149</v>
+        <v>198</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="B24" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>151</v>
+        <v>113</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>152</v>
+        <v>114</v>
       </c>
       <c r="B26" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>153</v>
+        <v>115</v>
       </c>
       <c r="B27" t="s">
-        <v>154</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>155</v>
+        <v>116</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>156</v>
+        <v>117</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>157</v>
+        <v>118</v>
       </c>
       <c r="B30" t="s">
-        <v>109</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>158</v>
+        <v>119</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>159</v>
+        <v>120</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>160</v>
+        <v>121</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>161</v>
+        <v>122</v>
       </c>
       <c r="B34" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>162</v>
+        <v>123</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>163</v>
+        <v>124</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>164</v>
+        <v>125</v>
       </c>
       <c r="B37" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="B38" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="B39" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>167</v>
+        <v>128</v>
       </c>
       <c r="B40" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="B41" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>169</v>
+        <v>130</v>
       </c>
       <c r="B42" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>170</v>
+        <v>131</v>
       </c>
       <c r="B43" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>171</v>
+        <v>132</v>
       </c>
       <c r="B44" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>172</v>
+        <v>124</v>
       </c>
       <c r="B45" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="B46" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="B47" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>175</v>
+        <v>127</v>
       </c>
       <c r="B48" t="s">
-        <v>39</v>
+        <v>199</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
       <c r="B49" t="s">
-        <v>121</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="B50" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="B51" t="s">
-        <v>41</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>178</v>
+        <v>137</v>
       </c>
       <c r="B52" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="B53" t="s">
-        <v>44</v>
+        <v>202</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>180</v>
+        <v>138</v>
       </c>
       <c r="B54" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>181</v>
+        <v>139</v>
       </c>
       <c r="B55" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>182</v>
+        <v>140</v>
       </c>
       <c r="B56" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>183</v>
+        <v>141</v>
       </c>
       <c r="B57" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>184</v>
+        <v>142</v>
       </c>
       <c r="B58" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>185</v>
+        <v>143</v>
       </c>
       <c r="B59" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>186</v>
+        <v>144</v>
       </c>
       <c r="B60" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>187</v>
+        <v>127</v>
       </c>
       <c r="B61" t="s">
-        <v>42</v>
+        <v>203</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="B62" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>189</v>
+        <v>146</v>
       </c>
       <c r="B63" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>190</v>
+        <v>147</v>
       </c>
       <c r="B64" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="B65" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B66" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="B67" t="s">
-        <v>56</v>
+        <v>205</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>164</v>
+        <v>124</v>
       </c>
       <c r="B68" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>194</v>
+        <v>149</v>
       </c>
       <c r="B69" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>195</v>
+        <v>150</v>
       </c>
       <c r="B70" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>196</v>
+        <v>151</v>
       </c>
       <c r="B71" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c r="B72" t="s">
-        <v>128</v>
+        <v>51</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>198</v>
+        <v>153</v>
       </c>
       <c r="B73" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="B74" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="B75" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>201</v>
+        <v>156</v>
       </c>
       <c r="B76" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>202</v>
+        <v>157</v>
       </c>
       <c r="B77" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>203</v>
+        <v>156</v>
       </c>
       <c r="B78" t="s">
-        <v>65</v>
+        <v>206</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>204</v>
+        <v>158</v>
       </c>
       <c r="B79" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B80" t="s">
-        <v>127</v>
+        <v>207</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>206</v>
+        <v>159</v>
       </c>
       <c r="B81" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>207</v>
+        <v>160</v>
       </c>
       <c r="B82" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>208</v>
+        <v>161</v>
       </c>
       <c r="B83" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>209</v>
+        <v>162</v>
       </c>
       <c r="B84" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>210</v>
+        <v>163</v>
       </c>
       <c r="B85" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>211</v>
+        <v>164</v>
       </c>
       <c r="B86" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B87" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>197</v>
+        <v>156</v>
       </c>
       <c r="B88" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>212</v>
+        <v>165</v>
       </c>
       <c r="B89" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>213</v>
+        <v>166</v>
       </c>
       <c r="B90" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>214</v>
+        <v>167</v>
       </c>
       <c r="B91" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="B92" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>216</v>
+        <v>169</v>
       </c>
       <c r="B93" t="s">
-        <v>117</v>
+        <v>47</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>217</v>
+        <v>170</v>
       </c>
       <c r="B94" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>218</v>
+        <v>171</v>
       </c>
       <c r="B95" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="B96" t="s">
-        <v>117</v>
+        <v>208</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>219</v>
+        <v>172</v>
       </c>
       <c r="B97" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>220</v>
+        <v>173</v>
       </c>
       <c r="B98" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>221</v>
+        <v>174</v>
       </c>
       <c r="B99" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>222</v>
+        <v>175</v>
       </c>
       <c r="B100" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>223</v>
+        <v>105</v>
       </c>
       <c r="B101" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>224</v>
+        <v>190</v>
       </c>
       <c r="B102" t="s">
-        <v>82</v>
+        <v>209</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>225</v>
+        <v>119</v>
       </c>
       <c r="B103" t="s">
-        <v>57</v>
+        <v>96</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="B104" t="s">
-        <v>126</v>
+        <v>210</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>226</v>
+        <v>176</v>
       </c>
       <c r="B105" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>227</v>
+        <v>177</v>
       </c>
       <c r="B106" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>228</v>
+        <v>178</v>
       </c>
       <c r="B107" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>229</v>
+        <v>179</v>
       </c>
       <c r="B108" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="B109" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>231</v>
+        <v>123</v>
       </c>
       <c r="B110" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>136</v>
+        <v>181</v>
       </c>
       <c r="B111" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="B112" t="s">
-        <v>123</v>
+        <v>78</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>232</v>
+        <v>183</v>
       </c>
       <c r="B113" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>233</v>
+        <v>101</v>
       </c>
       <c r="B114" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>234</v>
+        <v>184</v>
       </c>
       <c r="B115" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>235</v>
+        <v>162</v>
       </c>
       <c r="B116" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="B117" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>237</v>
+        <v>186</v>
       </c>
       <c r="B118" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>238</v>
+        <v>187</v>
       </c>
       <c r="B119" t="s">
-        <v>95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>239</v>
+        <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>163</v>
+        <v>211</v>
       </c>
       <c r="B121" t="s">
-        <v>97</v>
+        <v>212</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>240</v>
+        <v>213</v>
       </c>
       <c r="B122" t="s">
-        <v>98</v>
+        <v>214</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>139</v>
+        <v>215</v>
       </c>
       <c r="B123" t="s">
-        <v>124</v>
+        <v>216</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>241</v>
+        <v>164</v>
       </c>
       <c r="B124" t="s">
-        <v>99</v>
+        <v>217</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>242</v>
+        <v>218</v>
       </c>
       <c r="B125" t="s">
-        <v>100</v>
+        <v>219</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="B126" t="s">
-        <v>101</v>
+        <v>220</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>132</v>
+        <v>221</v>
       </c>
       <c r="B127" t="s">
-        <v>105</v>
+        <v>222</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="B128" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>131</v>
-      </c>
-      <c r="B129" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>216</v>
-      </c>
-      <c r="B130" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>245</v>
-      </c>
-      <c r="B131" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>246</v>
-      </c>
-      <c r="B132" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>247</v>
-      </c>
-      <c r="B133" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>157</v>
-      </c>
-      <c r="B134" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>141</v>
-      </c>
-      <c r="B135" t="s">
-        <v>119</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_tag.xlsx
+++ b/Avantis Mapping/SPARQL_tag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1DCE2D0-20A4-49E4-8C35-6663796E11B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0D9C3A-073F-40F9-8280-4AD7B8DEE0FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="242">
   <si>
     <t>TWONTO</t>
   </si>
@@ -518,9 +518,6 @@
     <t>http://www.toronto.ca/TWONTO#flowmeter</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#heater</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#collector_mechanism</t>
   </si>
   <si>
@@ -647,9 +644,6 @@
     <t>PI</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#blower_or_fan_with_drive</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#MV_electrical_cabinet</t>
   </si>
   <si>
@@ -717,6 +711,66 @@
   </si>
   <si>
     <t>WIT</t>
+  </si>
+  <si>
+    <t>WRT</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#motion_sensor_element</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#slude_density_meter</t>
+  </si>
+  <si>
+    <t>DIT</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#LV_electrical_panel</t>
+  </si>
+  <si>
+    <t>LP</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#battery_charger</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#blower</t>
+  </si>
+  <si>
+    <t>BL</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#fuel_burning_heater</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#SCBA</t>
+  </si>
+  <si>
+    <t>SCBA</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#protection_relay</t>
+  </si>
+  <si>
+    <t>AFR</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#5kV_electrical_cabinet</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#generator</t>
+  </si>
+  <si>
+    <t>GEN</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#air_silencer</t>
+  </si>
+  <si>
+    <t>SL</t>
   </si>
 </sst>
 </file>
@@ -829,8 +883,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}" name="Table1" displayName="Table1" ref="A2:B128" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B128" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}" name="Table1" displayName="Table1" ref="A2:B139" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B139" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{6954C25C-9295-466B-8916-09F7AE9B1E9C}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{C2EFA1BF-9094-4221-B7A9-7713F0DEA95D}" name="Tag"/>
@@ -1136,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B128"/>
+  <dimension ref="A1:B139"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56.7109375" bestFit="1" customWidth="1"/>
@@ -1201,7 +1255,7 @@
         <v>121</v>
       </c>
       <c r="B8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -1217,7 +1271,7 @@
         <v>121</v>
       </c>
       <c r="B10" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1230,938 +1284,1026 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>108</v>
+        <v>219</v>
       </c>
       <c r="B12" t="s">
-        <v>8</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>190</v>
+        <v>108</v>
       </c>
       <c r="B13" t="s">
-        <v>191</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>121</v>
+        <v>189</v>
       </c>
       <c r="B14" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B15" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>190</v>
+        <v>127</v>
       </c>
       <c r="B16" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>109</v>
+        <v>189</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>193</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="B18" t="s">
-        <v>195</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="B19" t="s">
-        <v>10</v>
+        <v>194</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>196</v>
+        <v>110</v>
       </c>
       <c r="B21" t="s">
-        <v>197</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>111</v>
+        <v>195</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>196</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>198</v>
+        <v>111</v>
       </c>
       <c r="B23" t="s">
-        <v>95</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>112</v>
+        <v>219</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>221</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>113</v>
+        <v>197</v>
       </c>
       <c r="B25" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B27" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B28" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B30" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>119</v>
+        <v>223</v>
       </c>
       <c r="B31" t="s">
-        <v>86</v>
+        <v>224</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B34" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B35" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B36" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B38" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B39" t="s">
-        <v>26</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B40" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B42" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B43" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B44" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>124</v>
+        <v>213</v>
       </c>
       <c r="B45" t="s">
-        <v>94</v>
+        <v>214</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B46" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>134</v>
+        <v>225</v>
       </c>
       <c r="B47" t="s">
-        <v>33</v>
+        <v>226</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B48" t="s">
-        <v>199</v>
+        <v>30</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B49" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B50" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>200</v>
+        <v>124</v>
       </c>
       <c r="B51" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B52" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>201</v>
+        <v>127</v>
       </c>
       <c r="B53" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B54" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B55" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B56" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>141</v>
+        <v>199</v>
       </c>
       <c r="B57" t="s">
-        <v>40</v>
+        <v>200</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B58" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B59" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B60" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="B61" t="s">
-        <v>203</v>
+        <v>40</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B62" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>146</v>
+        <v>227</v>
       </c>
       <c r="B63" t="s">
-        <v>45</v>
+        <v>228</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B64" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B65" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>198</v>
+        <v>127</v>
       </c>
       <c r="B66" t="s">
-        <v>98</v>
+        <v>201</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>204</v>
+        <v>145</v>
       </c>
       <c r="B67" t="s">
-        <v>205</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="B68" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B69" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B70" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>151</v>
+        <v>197</v>
       </c>
       <c r="B71" t="s">
-        <v>50</v>
+        <v>98</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>152</v>
+        <v>202</v>
       </c>
       <c r="B72" t="s">
-        <v>51</v>
+        <v>203</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>153</v>
+        <v>124</v>
       </c>
       <c r="B73" t="s">
-        <v>52</v>
+        <v>93</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>154</v>
+        <v>229</v>
       </c>
       <c r="B74" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B75" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B76" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>157</v>
+        <v>211</v>
       </c>
       <c r="B77" t="s">
-        <v>55</v>
+        <v>212</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B78" t="s">
-        <v>206</v>
+        <v>50</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="B79" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>204</v>
+        <v>153</v>
       </c>
       <c r="B80" t="s">
-        <v>207</v>
+        <v>52</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="B81" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B82" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B83" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>162</v>
+        <v>230</v>
       </c>
       <c r="B84" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="B85" t="s">
-        <v>59</v>
+        <v>204</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B86" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B87" t="s">
-        <v>97</v>
+        <v>205</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>156</v>
+        <v>230</v>
       </c>
       <c r="B88" t="s">
-        <v>91</v>
+        <v>231</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B89" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>166</v>
+        <v>232</v>
       </c>
       <c r="B90" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>167</v>
+        <v>233</v>
       </c>
       <c r="B91" t="s">
-        <v>63</v>
+        <v>234</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B92" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="B93" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="B94" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B95" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>196</v>
+        <v>163</v>
       </c>
       <c r="B96" t="s">
-        <v>208</v>
+        <v>60</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="B97" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>173</v>
+        <v>156</v>
       </c>
       <c r="B98" t="s">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="B99" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>175</v>
+        <v>235</v>
       </c>
       <c r="B100" t="s">
-        <v>70</v>
+        <v>236</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>105</v>
+        <v>209</v>
       </c>
       <c r="B101" t="s">
-        <v>87</v>
+        <v>210</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="B102" t="s">
-        <v>209</v>
+        <v>62</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>119</v>
+        <v>166</v>
       </c>
       <c r="B103" t="s">
-        <v>96</v>
+        <v>63</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>190</v>
+        <v>167</v>
       </c>
       <c r="B104" t="s">
-        <v>210</v>
+        <v>64</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="B105" t="s">
-        <v>71</v>
+        <v>47</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B106" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="B107" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="B108" t="s">
-        <v>74</v>
+        <v>206</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="B109" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="B110" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="B111" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>182</v>
+        <v>237</v>
       </c>
       <c r="B112" t="s">
-        <v>78</v>
+        <v>200</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="B113" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B114" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="B115" t="s">
-        <v>80</v>
+        <v>207</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>162</v>
+        <v>119</v>
       </c>
       <c r="B116" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B117" t="s">
-        <v>81</v>
+        <v>208</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="B118" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>187</v>
+        <v>238</v>
       </c>
       <c r="B119" t="s">
-        <v>1</v>
+        <v>239</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>119</v>
+        <v>176</v>
       </c>
       <c r="B120" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>211</v>
+        <v>177</v>
       </c>
       <c r="B121" t="s">
-        <v>212</v>
+        <v>73</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="B122" t="s">
-        <v>214</v>
+        <v>74</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>215</v>
+        <v>179</v>
       </c>
       <c r="B123" t="s">
-        <v>216</v>
+        <v>75</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>164</v>
+        <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>217</v>
+        <v>76</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>218</v>
+        <v>180</v>
       </c>
       <c r="B125" t="s">
-        <v>219</v>
+        <v>77</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
+        <v>216</v>
+      </c>
+      <c r="B126" t="s">
         <v>218</v>
-      </c>
-      <c r="B126" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="B127" t="s">
-        <v>222</v>
+        <v>78</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>221</v>
+        <v>182</v>
       </c>
       <c r="B128" t="s">
-        <v>223</v>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>163</v>
+      </c>
+      <c r="B129" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>101</v>
+      </c>
+      <c r="B130" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>216</v>
+      </c>
+      <c r="B131" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>183</v>
+      </c>
+      <c r="B132" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>161</v>
+      </c>
+      <c r="B133" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>184</v>
+      </c>
+      <c r="B134" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>185</v>
+      </c>
+      <c r="B135" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>186</v>
+      </c>
+      <c r="B136" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>119</v>
+      </c>
+      <c r="B137" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>219</v>
+      </c>
+      <c r="B138" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>240</v>
+      </c>
+      <c r="B139" t="s">
+        <v>241</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_tag.xlsx
+++ b/Avantis Mapping/SPARQL_tag.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D0D9C3A-073F-40F9-8280-4AD7B8DEE0FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A642DFE-1A47-4251-BF14-5A2FD8D74232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -239,9 +239,6 @@
     <t>T</t>
   </si>
   <si>
-    <t>WR</t>
-  </si>
-  <si>
     <t>VIT</t>
   </si>
   <si>
@@ -434,9 +431,6 @@
     <t>http://www.toronto.ca/TWONTO#transformer</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#flow_element</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#fixed_gas_detector</t>
   </si>
   <si>
@@ -509,9 +503,6 @@
     <t>http://www.toronto.ca/TWONTO#variable_air_volume_unit</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#burner_component_of_asset</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#flow_switch</t>
   </si>
   <si>
@@ -521,9 +512,6 @@
     <t>http://www.toronto.ca/TWONTO#collector_mechanism</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#controller</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#material_distribution_panel</t>
   </si>
   <si>
@@ -560,9 +548,6 @@
     <t>http://www.toronto.ca/TWONTO#storage_tank</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#welding_receptacle</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#vibration_analyzer</t>
   </si>
   <si>
@@ -578,15 +563,9 @@
     <t>http://www.toronto.ca/TWONTO#conveyor</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#equipment_or_access_chamber</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#hydraulic_power_pack</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#large_stationary_tool</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#surge_suppressor</t>
   </si>
   <si>
@@ -644,12 +623,6 @@
     <t>PI</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#MV_electrical_cabinet</t>
-  </si>
-  <si>
-    <t>BUS</t>
-  </si>
-  <si>
     <t>TI</t>
   </si>
   <si>
@@ -728,9 +701,6 @@
     <t>DIT</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#LV_electrical_panel</t>
-  </si>
-  <si>
     <t>LP</t>
   </si>
   <si>
@@ -743,9 +713,6 @@
     <t>BL</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#fuel_burning_heater</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#SCBA</t>
   </si>
   <si>
@@ -758,9 +725,6 @@
     <t>AFR</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#5kV_electrical_cabinet</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#generator</t>
   </si>
   <si>
@@ -771,6 +735,42 @@
   </si>
   <si>
     <t>SL</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#burner_-_component_of_asset</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#process_controller</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#flow_sensor_element</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#heater</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#lighting_panel</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#chemical_dosing_system</t>
+  </si>
+  <si>
+    <t>FD</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#equipment_chamber_or_access_chamber</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#torque_switch</t>
+  </si>
+  <si>
+    <t>XSH</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#stationary_tool</t>
+  </si>
+  <si>
+    <t>RTU</t>
   </si>
 </sst>
 </file>
@@ -1191,1119 +1191,1119 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
   <dimension ref="A1:B139"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="56.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="56.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="165" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B8" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>105</v>
-      </c>
-      <c r="B7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>121</v>
-      </c>
-      <c r="B8" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>106</v>
       </c>
       <c r="B9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B10" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="B12" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B14" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B15" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B19" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B21" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B22" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="B24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="B25" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B27" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>230</v>
+      </c>
+      <c r="B28" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
         <v>114</v>
       </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="B30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>115</v>
       </c>
-      <c r="B29" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="B31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>214</v>
+      </c>
+      <c r="B32" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>116</v>
       </c>
-      <c r="B30" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>223</v>
-      </c>
-      <c r="B31" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="B33" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>117</v>
       </c>
-      <c r="B32" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="B34" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>118</v>
       </c>
-      <c r="B33" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="B35" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>119</v>
       </c>
-      <c r="B34" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
+      <c r="B36" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
         <v>120</v>
       </c>
-      <c r="B35" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="B37" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
         <v>121</v>
       </c>
-      <c r="B36" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="B38" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>122</v>
       </c>
-      <c r="B37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
+      <c r="B39" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>123</v>
       </c>
-      <c r="B38" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
+      <c r="B40" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
         <v>124</v>
       </c>
-      <c r="B39" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
+      <c r="B41" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>231</v>
+      </c>
+      <c r="B42" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
         <v>125</v>
       </c>
-      <c r="B40" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
+      <c r="B43" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
         <v>126</v>
       </c>
-      <c r="B41" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
+      <c r="B44" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
         <v>127</v>
       </c>
-      <c r="B42" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
+      <c r="B45" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>204</v>
+      </c>
+      <c r="B46" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>128</v>
       </c>
-      <c r="B43" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="B47" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>216</v>
+      </c>
+      <c r="B48" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>129</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B49" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>130</v>
+      </c>
+      <c r="B50" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>131</v>
+      </c>
+      <c r="B51" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>123</v>
+      </c>
+      <c r="B52" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>232</v>
+      </c>
+      <c r="B53" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>213</v>
-      </c>
-      <c r="B45" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>130</v>
-      </c>
-      <c r="B46" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>225</v>
-      </c>
-      <c r="B47" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>131</v>
-      </c>
-      <c r="B48" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>132</v>
       </c>
-      <c r="B49" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="B54" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>126</v>
+      </c>
+      <c r="B55" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
         <v>133</v>
       </c>
-      <c r="B50" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>124</v>
-      </c>
-      <c r="B51" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="B56" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
         <v>134</v>
       </c>
-      <c r="B52" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>127</v>
-      </c>
-      <c r="B53" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="B57" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>135</v>
       </c>
-      <c r="B54" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
+      <c r="B58" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
         <v>136</v>
       </c>
-      <c r="B55" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
+      <c r="B59" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>137</v>
       </c>
-      <c r="B56" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>199</v>
-      </c>
-      <c r="B57" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
+      <c r="B60" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>138</v>
       </c>
-      <c r="B58" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
+      <c r="B61" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>139</v>
       </c>
-      <c r="B59" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+      <c r="B62" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>140</v>
       </c>
-      <c r="B60" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
+      <c r="B63" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>141</v>
-      </c>
-      <c r="B61" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>142</v>
-      </c>
-      <c r="B62" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>227</v>
-      </c>
-      <c r="B63" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>143</v>
       </c>
       <c r="B64" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B65" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B66" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B67" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
+        <v>228</v>
+      </c>
+      <c r="B68" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>144</v>
+      </c>
+      <c r="B69" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>145</v>
+      </c>
+      <c r="B70" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
         <v>146</v>
       </c>
-      <c r="B68" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
+      <c r="B71" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>190</v>
+      </c>
+      <c r="B72" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>193</v>
+      </c>
+      <c r="B73" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>123</v>
+      </c>
+      <c r="B74" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>219</v>
+      </c>
+      <c r="B75" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
         <v>147</v>
       </c>
-      <c r="B69" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
+      <c r="B76" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
         <v>148</v>
       </c>
-      <c r="B70" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>197</v>
-      </c>
-      <c r="B71" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
+      <c r="B77" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
         <v>202</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B78" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>124</v>
-      </c>
-      <c r="B73" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>229</v>
-      </c>
-      <c r="B74" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
         <v>149</v>
       </c>
-      <c r="B75" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
+      <c r="B79" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
         <v>150</v>
       </c>
-      <c r="B76" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>211</v>
-      </c>
-      <c r="B77" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
+      <c r="B80" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
         <v>151</v>
       </c>
-      <c r="B78" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+      <c r="B81" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
         <v>152</v>
-      </c>
-      <c r="B79" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>153</v>
-      </c>
-      <c r="B80" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>154</v>
-      </c>
-      <c r="B81" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>155</v>
       </c>
       <c r="B82" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B83" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B84" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>156</v>
+        <v>233</v>
       </c>
       <c r="B85" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B86" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>154</v>
+      </c>
+      <c r="B87" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>202</v>
-      </c>
-      <c r="B87" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="B88" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>158</v>
+        <v>220</v>
       </c>
       <c r="B89" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B90" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="B91" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="B92" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B93" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B94" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B95" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="B96" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
+        <v>190</v>
+      </c>
+      <c r="B97" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>153</v>
+      </c>
+      <c r="B98" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>235</v>
+      </c>
+      <c r="B99" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>160</v>
+      </c>
+      <c r="B100" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>224</v>
+      </c>
+      <c r="B101" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102" t="s">
+        <v>200</v>
+      </c>
+      <c r="B102" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103" t="s">
+        <v>161</v>
+      </c>
+      <c r="B103" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>162</v>
+      </c>
+      <c r="B104" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>163</v>
+      </c>
+      <c r="B105" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A106" t="s">
+        <v>164</v>
+      </c>
+      <c r="B106" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A107" t="s">
+        <v>165</v>
+      </c>
+      <c r="B107" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A108" t="s">
+        <v>166</v>
+      </c>
+      <c r="B108" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A109" t="s">
+        <v>188</v>
+      </c>
+      <c r="B109" t="s">
         <v>197</v>
       </c>
-      <c r="B97" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>156</v>
-      </c>
-      <c r="B98" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>164</v>
-      </c>
-      <c r="B99" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>235</v>
-      </c>
-      <c r="B100" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>209</v>
-      </c>
-      <c r="B101" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>165</v>
-      </c>
-      <c r="B102" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>166</v>
-      </c>
-      <c r="B103" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A110" t="s">
         <v>167</v>
       </c>
-      <c r="B104" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
+      <c r="B110" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A111" t="s">
         <v>168</v>
       </c>
-      <c r="B105" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
+      <c r="B111" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A112" t="s">
         <v>169</v>
       </c>
-      <c r="B106" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+      <c r="B112" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A113" t="s">
+        <v>104</v>
+      </c>
+      <c r="B113" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A114" t="s">
+        <v>182</v>
+      </c>
+      <c r="B114" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A115" t="s">
+        <v>118</v>
+      </c>
+      <c r="B115" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A116" t="s">
+        <v>237</v>
+      </c>
+      <c r="B116" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A117" t="s">
+        <v>182</v>
+      </c>
+      <c r="B117" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A118" t="s">
+        <v>238</v>
+      </c>
+      <c r="B118" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A119" t="s">
         <v>170</v>
       </c>
-      <c r="B107" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>195</v>
-      </c>
-      <c r="B108" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
+      <c r="B119" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A120" t="s">
+        <v>226</v>
+      </c>
+      <c r="B120" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A121" t="s">
         <v>171</v>
       </c>
-      <c r="B109" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
+      <c r="B121" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A122" t="s">
         <v>172</v>
       </c>
-      <c r="B110" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>173</v>
-      </c>
-      <c r="B111" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>237</v>
-      </c>
-      <c r="B112" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" t="s">
-        <v>174</v>
-      </c>
-      <c r="B113" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" t="s">
-        <v>105</v>
-      </c>
-      <c r="B114" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115" t="s">
-        <v>189</v>
-      </c>
-      <c r="B115" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" t="s">
-        <v>119</v>
-      </c>
-      <c r="B116" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>189</v>
-      </c>
-      <c r="B117" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
-        <v>175</v>
-      </c>
-      <c r="B118" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" t="s">
-        <v>238</v>
-      </c>
-      <c r="B119" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" t="s">
-        <v>176</v>
-      </c>
-      <c r="B120" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" t="s">
-        <v>177</v>
-      </c>
-      <c r="B121" t="s">
+      <c r="B122" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122" t="s">
-        <v>178</v>
-      </c>
-      <c r="B122" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>179</v>
+        <v>122</v>
       </c>
       <c r="B123" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>123</v>
+        <v>173</v>
       </c>
       <c r="B124" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="B125" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
+        <v>174</v>
+      </c>
+      <c r="B126" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A126" t="s">
-        <v>216</v>
-      </c>
-      <c r="B126" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>181</v>
+        <v>240</v>
       </c>
       <c r="B127" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A128" t="s">
+        <v>175</v>
+      </c>
+      <c r="B128" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A128" t="s">
-        <v>182</v>
-      </c>
-      <c r="B128" t="s">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A129" t="s">
+        <v>159</v>
+      </c>
+      <c r="B129" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A130" t="s">
+        <v>100</v>
+      </c>
+      <c r="B130" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>207</v>
+      </c>
+      <c r="B131" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A132" t="s">
+        <v>176</v>
+      </c>
+      <c r="B132" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
-        <v>163</v>
-      </c>
-      <c r="B129" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
-        <v>101</v>
-      </c>
-      <c r="B130" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
-        <v>216</v>
-      </c>
-      <c r="B131" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>183</v>
-      </c>
-      <c r="B132" t="s">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A133" t="s">
+        <v>157</v>
+      </c>
+      <c r="B133" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A134" t="s">
+        <v>177</v>
+      </c>
+      <c r="B134" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133" t="s">
-        <v>161</v>
-      </c>
-      <c r="B133" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>184</v>
-      </c>
-      <c r="B134" t="s">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A135" t="s">
+        <v>178</v>
+      </c>
+      <c r="B135" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>185</v>
-      </c>
-      <c r="B135" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="B136" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B137" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="B138" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="B139" t="s">
-        <v>241</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_tag.xlsx
+++ b/Avantis Mapping/SPARQL_tag.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A642DFE-1A47-4251-BF14-5A2FD8D74232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF9F43A-23C7-48CF-947D-1D9360FF7AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10360" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -290,487 +290,487 @@
     <t>Tag</t>
   </si>
   <si>
+    <t>PCV</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>FCV</t>
+  </si>
+  <si>
+    <t>FT</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>FIT</t>
+  </si>
+  <si>
+    <t>PIT</t>
+  </si>
+  <si>
+    <t>LRT</t>
+  </si>
+  <si>
+    <t>LIT</t>
+  </si>
+  <si>
+    <t>ZT</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>ZIT</t>
+  </si>
+  <si>
+    <t>ZRT</t>
+  </si>
+  <si>
+    <t>FN</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#AC_evaporator_unit</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#instrument_sensor_element</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#chlorinator_system</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#ozone_generator</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#gearbox</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#pressure_transmitter</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#clarifier</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#pressurized_sewer_segment</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#channel_gate</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#security_camera</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#dehumidifier</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#engine</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#pipe_segment</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#chiller</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#centrifuge</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#air_handler_unit</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#auto_sampler</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#automatic_external_defibrillator</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#operator_interface_terminal</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#valve</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#elevator</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#level_switch</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#power_washer</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#display_panel</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#level_transmitter</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#roll_up_door</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#UV_disinfection_assembly</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#instrument_gauge_or_display</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#transformer</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#fixed_gas_detector</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#strainer</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#air_scrubber</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#grinder_or_comminutor</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#air_condition</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#heat_exchanger</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#computer</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#AC_condenser_unit</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#instrument_transmitter</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#ejector</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#condensate_trap</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#classifier</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#flame_arrestor</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#outfall_or_discharge_point</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#air_duct_segment</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#hydrant</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#dust_collector</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#fire_rated_door</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#screen</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#mixer_or_agitator</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#UPS</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#furnace</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#reservoir_tank</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#variable_air_volume_unit</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#flow_switch</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#flowmeter</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#collector_mechanism</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#material_distribution_panel</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#controlled_door_access</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#flow_transmitter</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#server_appliance</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#motor</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#quencher</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#transfer_switch</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#reactor</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#trap_priming_device</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#battery</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#ash_lagoon</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#storage_tank</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#vibration_analyzer</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#compressor</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#air_damper</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#boiler</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#conveyor</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#hydraulic_power_pack</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#surge_suppressor</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#backflow_preventer</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#annunciator_panel</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#ladder</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#data_logger</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#ground_and_test_device</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#humidifier</t>
+  </si>
+  <si>
+    <t>LSHH</t>
+  </si>
+  <si>
+    <t>LSLL</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#pressure_switch</t>
+  </si>
+  <si>
+    <t>PSH</t>
+  </si>
+  <si>
+    <t>LSL</t>
+  </si>
+  <si>
+    <t>LI</t>
+  </si>
+  <si>
+    <t>PSL</t>
+  </si>
+  <si>
+    <t>LSH</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#temperature_transmitter</t>
+  </si>
+  <si>
+    <t>TIT</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#position_sensing</t>
+  </si>
+  <si>
+    <t>PI</t>
+  </si>
+  <si>
+    <t>TI</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#temperature_switch</t>
+  </si>
+  <si>
+    <t>TSH</t>
+  </si>
+  <si>
+    <t>FQ</t>
+  </si>
+  <si>
+    <t>TSL</t>
+  </si>
+  <si>
+    <t>TT</t>
+  </si>
+  <si>
+    <t>PSLL</t>
+  </si>
+  <si>
+    <t>PSHH</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#process_control_panel</t>
+  </si>
+  <si>
+    <t>CP</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#RPU_panel</t>
+  </si>
+  <si>
+    <t>RPU</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#cable_segment</t>
+  </si>
+  <si>
+    <t>CBL</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#position_switch</t>
+  </si>
+  <si>
+    <t>ZSH</t>
+  </si>
+  <si>
+    <t>ZSL</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#weight_scale</t>
+  </si>
+  <si>
+    <t>WSC</t>
+  </si>
+  <si>
+    <t>WIT</t>
+  </si>
+  <si>
+    <t>WRT</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#motion_sensor_element</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>DIT</t>
+  </si>
+  <si>
+    <t>LP</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#battery_charger</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#blower</t>
+  </si>
+  <si>
+    <t>BL</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#SCBA</t>
+  </si>
+  <si>
+    <t>SCBA</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#protection_relay</t>
+  </si>
+  <si>
+    <t>AFR</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#generator</t>
+  </si>
+  <si>
+    <t>GEN</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#air_silencer</t>
+  </si>
+  <si>
+    <t>SL</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#burner_-_component_of_asset</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#process_controller</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#flow_sensor_element</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#heater</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#lighting_panel</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#chemical_dosing_system</t>
+  </si>
+  <si>
+    <t>FD</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#equipment_chamber_or_access_chamber</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#torque_switch</t>
+  </si>
+  <si>
+    <t>XSH</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#stationary_tool</t>
+  </si>
+  <si>
+    <t>RTU</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#sludge_density_meter</t>
+  </si>
+  <si>
     <t>PREFIX rdf: &lt;http://www.w3.org/1999/02/22-rdf-syntax-ns#&gt;
 PREFIX owl: &lt;http://www.w3.org/2002/07/owl#&gt;
 PREFIX rdfs: &lt;http://www.w3.org/2000/01/rdf-schema#&gt;
 PREFIX xsd: &lt;http://www.w3.org/2001/XMLSchema#&gt;
 PREFIX tw: &lt;http://www.toronto.ca/TWONTO#&gt;
-SELECT (STR(?label) as ?TWONTO) (STR(?object) as ?Avantis)
+SELECT ?TWONTO (STR(?object) as ?Avantis)
 WHERE { 
-    ?entityIRI tw:is_equivalent_to_tag_code ?object ;
-              rdfs:label ?label .
+    ?TWONTO tw:is_equivalent_to_tag_code ?object .
+    FILTER NOT EXISTS { ?TWONTO owl:deprecated "true"^^xsd:boolean }
 }</t>
-  </si>
-  <si>
-    <t>PCV</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>FCV</t>
-  </si>
-  <si>
-    <t>FT</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>FIT</t>
-  </si>
-  <si>
-    <t>PIT</t>
-  </si>
-  <si>
-    <t>LRT</t>
-  </si>
-  <si>
-    <t>LIT</t>
-  </si>
-  <si>
-    <t>ZT</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>ZIT</t>
-  </si>
-  <si>
-    <t>ZRT</t>
-  </si>
-  <si>
-    <t>FN</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#AC_evaporator_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_sensor_element</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#chlorinator_system</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#ozone_generator</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#gearbox</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pressure_transmitter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#clarifier</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pressurized_sewer_segment</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#channel_gate</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#security_camera</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#dehumidifier</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#engine</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pipe_segment</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#chiller</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#centrifuge</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_handler_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#auto_sampler</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#automatic_external_defibrillator</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#operator_interface_terminal</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#valve</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#elevator</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#level_switch</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#power_washer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#display_panel</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#level_transmitter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#roll_up_door</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#UV_disinfection_assembly</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_gauge_or_display</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#transformer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#fixed_gas_detector</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#strainer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_scrubber</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#grinder_or_comminutor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_condition</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#heat_exchanger</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#computer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#AC_condenser_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_transmitter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#ejector</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#condensate_trap</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#classifier</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#flame_arrestor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#outfall_or_discharge_point</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_duct_segment</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#hydrant</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#dust_collector</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#fire_rated_door</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#screen</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#mixer_or_agitator</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#UPS</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#furnace</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#reservoir_tank</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#variable_air_volume_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#flow_switch</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#flowmeter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#collector_mechanism</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#material_distribution_panel</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#controlled_door_access</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#flow_transmitter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#server_appliance</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#motor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#quencher</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#transfer_switch</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#reactor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#trap_priming_device</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#battery</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#ash_lagoon</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#storage_tank</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#vibration_analyzer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#compressor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_damper</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#boiler</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#conveyor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#hydraulic_power_pack</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#surge_suppressor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#backflow_preventer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#annunciator_panel</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#ladder</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#data_logger</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#ground_and_test_device</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#humidifier</t>
-  </si>
-  <si>
-    <t>LSHH</t>
-  </si>
-  <si>
-    <t>LSLL</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pressure_switch</t>
-  </si>
-  <si>
-    <t>PSH</t>
-  </si>
-  <si>
-    <t>LSL</t>
-  </si>
-  <si>
-    <t>LI</t>
-  </si>
-  <si>
-    <t>PSL</t>
-  </si>
-  <si>
-    <t>LSH</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#temperature_transmitter</t>
-  </si>
-  <si>
-    <t>TIT</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#position_sensing</t>
-  </si>
-  <si>
-    <t>PI</t>
-  </si>
-  <si>
-    <t>TI</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#temperature_switch</t>
-  </si>
-  <si>
-    <t>TSH</t>
-  </si>
-  <si>
-    <t>FQ</t>
-  </si>
-  <si>
-    <t>TSL</t>
-  </si>
-  <si>
-    <t>TT</t>
-  </si>
-  <si>
-    <t>PSLL</t>
-  </si>
-  <si>
-    <t>PSHH</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#process_control_panel</t>
-  </si>
-  <si>
-    <t>CP</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#RPU_panel</t>
-  </si>
-  <si>
-    <t>RPU</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#cable_segment</t>
-  </si>
-  <si>
-    <t>CBL</t>
-  </si>
-  <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#position_switch</t>
-  </si>
-  <si>
-    <t>ZSH</t>
-  </si>
-  <si>
-    <t>ZSL</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#weight_scale</t>
-  </si>
-  <si>
-    <t>WSC</t>
-  </si>
-  <si>
-    <t>WIT</t>
-  </si>
-  <si>
-    <t>WRT</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#motion_sensor_element</t>
-  </si>
-  <si>
-    <t>MS</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#slude_density_meter</t>
-  </si>
-  <si>
-    <t>DIT</t>
-  </si>
-  <si>
-    <t>LP</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#battery_charger</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#blower</t>
-  </si>
-  <si>
-    <t>BL</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#SCBA</t>
-  </si>
-  <si>
-    <t>SCBA</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#protection_relay</t>
-  </si>
-  <si>
-    <t>AFR</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#generator</t>
-  </si>
-  <si>
-    <t>GEN</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_silencer</t>
-  </si>
-  <si>
-    <t>SL</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#burner_-_component_of_asset</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#process_controller</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#flow_sensor_element</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#heater</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#lighting_panel</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#chemical_dosing_system</t>
-  </si>
-  <si>
-    <t>FD</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#equipment_chamber_or_access_chamber</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#torque_switch</t>
-  </si>
-  <si>
-    <t>XSH</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#stationary_tool</t>
-  </si>
-  <si>
-    <t>RTU</t>
   </si>
 </sst>
 </file>
@@ -1197,9 +1197,9 @@
     <col min="2" max="2" width="61.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="174" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>84</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1212,7 +1212,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
@@ -1220,7 +1220,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B4" t="s">
         <v>2</v>
@@ -1228,7 +1228,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s">
         <v>3</v>
@@ -1236,7 +1236,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s">
         <v>4</v>
@@ -1244,23 +1244,23 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B9" t="s">
         <v>5</v>
@@ -1268,15 +1268,15 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
@@ -1284,15 +1284,15 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
@@ -1300,39 +1300,39 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B14" t="s">
         <v>182</v>
-      </c>
-      <c r="B14" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B18" t="s">
         <v>9</v>
@@ -1340,15 +1340,15 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B19" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B20" t="s">
         <v>10</v>
@@ -1356,7 +1356,7 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B21" t="s">
         <v>11</v>
@@ -1364,15 +1364,15 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>187</v>
+      </c>
+      <c r="B22" t="s">
         <v>188</v>
-      </c>
-      <c r="B22" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -1380,23 +1380,23 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B24" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B25" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
@@ -1404,7 +1404,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B27" t="s">
         <v>15</v>
@@ -1412,7 +1412,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B28" t="s">
         <v>53</v>
@@ -1420,7 +1420,7 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B29" t="s">
         <v>16</v>
@@ -1428,7 +1428,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B30" t="s">
         <v>17</v>
@@ -1436,7 +1436,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B31" t="s">
         <v>18</v>
@@ -1444,15 +1444,15 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
+        <v>213</v>
+      </c>
+      <c r="B32" t="s">
         <v>214</v>
-      </c>
-      <c r="B32" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B33" t="s">
         <v>19</v>
@@ -1460,7 +1460,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B34" t="s">
         <v>36</v>
@@ -1468,15 +1468,15 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B35" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B36" t="s">
         <v>20</v>
@@ -1484,7 +1484,7 @@
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B37" t="s">
         <v>21</v>
@@ -1492,7 +1492,7 @@
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B38" t="s">
         <v>22</v>
@@ -1500,7 +1500,7 @@
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B39" t="s">
         <v>23</v>
@@ -1508,15 +1508,15 @@
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B40" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B41" t="s">
         <v>24</v>
@@ -1524,7 +1524,7 @@
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B42" t="s">
         <v>57</v>
@@ -1532,7 +1532,7 @@
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B43" t="s">
         <v>25</v>
@@ -1540,7 +1540,7 @@
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B44" t="s">
         <v>26</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B45" t="s">
         <v>27</v>
@@ -1556,15 +1556,15 @@
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
+        <v>203</v>
+      </c>
+      <c r="B46" t="s">
         <v>204</v>
-      </c>
-      <c r="B46" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B47" t="s">
         <v>29</v>
@@ -1572,15 +1572,15 @@
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="B48" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B49" t="s">
         <v>30</v>
@@ -1588,7 +1588,7 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B50" t="s">
         <v>31</v>
@@ -1596,7 +1596,7 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B51" t="s">
         <v>32</v>
@@ -1604,15 +1604,15 @@
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B52" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B53" t="s">
         <v>28</v>
@@ -1620,7 +1620,7 @@
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B54" t="s">
         <v>33</v>
@@ -1628,15 +1628,15 @@
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B55" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B56" t="s">
         <v>34</v>
@@ -1644,7 +1644,7 @@
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B57" t="s">
         <v>35</v>
@@ -1652,7 +1652,7 @@
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B58" t="s">
         <v>12</v>
@@ -1660,7 +1660,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B59" t="s">
         <v>37</v>
@@ -1668,7 +1668,7 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B60" t="s">
         <v>38</v>
@@ -1676,7 +1676,7 @@
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B61" t="s">
         <v>39</v>
@@ -1684,7 +1684,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B62" t="s">
         <v>40</v>
@@ -1692,7 +1692,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B63" t="s">
         <v>41</v>
@@ -1700,7 +1700,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B64" t="s">
         <v>42</v>
@@ -1708,7 +1708,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B65" t="s">
         <v>43</v>
@@ -1716,15 +1716,15 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B66" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B67" t="s">
         <v>44</v>
@@ -1732,15 +1732,15 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B68" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B69" t="s">
         <v>45</v>
@@ -1748,7 +1748,7 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B70" t="s">
         <v>24</v>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B71" t="s">
         <v>46</v>
@@ -1764,31 +1764,31 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B72" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
+        <v>192</v>
+      </c>
+      <c r="B73" t="s">
         <v>193</v>
-      </c>
-      <c r="B73" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B74" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B75" t="s">
         <v>47</v>
@@ -1796,7 +1796,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B76" t="s">
         <v>48</v>
@@ -1804,7 +1804,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B77" t="s">
         <v>49</v>
@@ -1812,15 +1812,15 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
+        <v>201</v>
+      </c>
+      <c r="B78" t="s">
         <v>202</v>
-      </c>
-      <c r="B78" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B79" t="s">
         <v>50</v>
@@ -1828,7 +1828,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B80" t="s">
         <v>51</v>
@@ -1836,7 +1836,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B81" t="s">
         <v>52</v>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B82" t="s">
         <v>54</v>
@@ -1852,23 +1852,23 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B83" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B84" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B85" t="s">
         <v>55</v>
@@ -1876,15 +1876,15 @@
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B86" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B87" t="s">
         <v>56</v>
@@ -1892,39 +1892,39 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B88" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B89" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B90" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B91" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B92" t="s">
         <v>58</v>
@@ -1932,7 +1932,7 @@
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B93" t="s">
         <v>24</v>
@@ -1940,15 +1940,15 @@
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B94" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B95" t="s">
         <v>59</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B96" t="s">
         <v>60</v>
@@ -1964,31 +1964,31 @@
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B97" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B98" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B99" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B100" t="s">
         <v>61</v>
@@ -1996,23 +1996,23 @@
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B101" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
+        <v>199</v>
+      </c>
+      <c r="B102" t="s">
         <v>200</v>
-      </c>
-      <c r="B102" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B103" t="s">
         <v>62</v>
@@ -2020,7 +2020,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B104" t="s">
         <v>63</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B105" t="s">
         <v>64</v>
@@ -2036,7 +2036,7 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B106" t="s">
         <v>47</v>
@@ -2044,7 +2044,7 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B107" t="s">
         <v>65</v>
@@ -2052,7 +2052,7 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B108" t="s">
         <v>66</v>
@@ -2060,15 +2060,15 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B109" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B110" t="s">
         <v>67</v>
@@ -2076,7 +2076,7 @@
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B111" t="s">
         <v>68</v>
@@ -2084,7 +2084,7 @@
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B112" t="s">
         <v>69</v>
@@ -2092,31 +2092,31 @@
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B113" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B114" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B115" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B116" t="s">
         <v>72</v>
@@ -2124,23 +2124,23 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B117" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B118" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B119" t="s">
         <v>70</v>
@@ -2148,15 +2148,15 @@
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B120" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B121" t="s">
         <v>71</v>
@@ -2164,7 +2164,7 @@
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B122" t="s">
         <v>73</v>
@@ -2172,7 +2172,7 @@
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B123" t="s">
         <v>75</v>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B124" t="s">
         <v>76</v>
@@ -2188,15 +2188,15 @@
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B125" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B126" t="s">
         <v>77</v>
@@ -2204,7 +2204,7 @@
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B127" t="s">
         <v>74</v>
@@ -2212,7 +2212,7 @@
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B128" t="s">
         <v>78</v>
@@ -2220,15 +2220,15 @@
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B129" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B130" t="s">
         <v>82</v>
@@ -2236,15 +2236,15 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
+        <v>206</v>
+      </c>
+      <c r="B131" t="s">
         <v>207</v>
-      </c>
-      <c r="B131" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B132" t="s">
         <v>79</v>
@@ -2252,15 +2252,15 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B133" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B134" t="s">
         <v>80</v>
@@ -2268,7 +2268,7 @@
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B135" t="s">
         <v>81</v>
@@ -2276,7 +2276,7 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B136" t="s">
         <v>1</v>
@@ -2284,26 +2284,26 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B137" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B138" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>210</v>
+        <v>240</v>
       </c>
       <c r="B139" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_tag.xlsx
+++ b/Avantis Mapping/SPARQL_tag.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF9F43A-23C7-48CF-947D-1D9360FF7AC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DB0E92-83C4-401E-BF2A-42FEC5D009D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10360" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="255">
   <si>
     <t>TWONTO</t>
   </si>
@@ -575,30 +575,9 @@
     <t>http://www.toronto.ca/TWONTO#humidifier</t>
   </si>
   <si>
-    <t>LSHH</t>
-  </si>
-  <si>
-    <t>LSLL</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pressure_switch</t>
-  </si>
-  <si>
-    <t>PSH</t>
-  </si>
-  <si>
-    <t>LSL</t>
-  </si>
-  <si>
     <t>LI</t>
   </si>
   <si>
-    <t>PSL</t>
-  </si>
-  <si>
-    <t>LSH</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#temperature_transmitter</t>
   </si>
   <si>
@@ -614,27 +593,12 @@
     <t>TI</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#temperature_switch</t>
-  </si>
-  <si>
-    <t>TSH</t>
-  </si>
-  <si>
     <t>FQ</t>
   </si>
   <si>
-    <t>TSL</t>
-  </si>
-  <si>
     <t>TT</t>
   </si>
   <si>
-    <t>PSLL</t>
-  </si>
-  <si>
-    <t>PSHH</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#process_control_panel</t>
   </si>
   <si>
@@ -653,18 +617,6 @@
     <t>CBL</t>
   </si>
   <si>
-    <t>M</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#position_switch</t>
-  </si>
-  <si>
-    <t>ZSH</t>
-  </si>
-  <si>
-    <t>ZSL</t>
-  </si>
-  <si>
     <t>http://www.toronto.ca/TWONTO#weight_scale</t>
   </si>
   <si>
@@ -714,12 +666,6 @@
   </si>
   <si>
     <t>GEN</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_silencer</t>
-  </si>
-  <si>
-    <t>SL</t>
   </si>
   <si>
     <t>http://www.toronto.ca/TWONTO#burner_-_component_of_asset</t>
@@ -771,6 +717,99 @@
     ?TWONTO tw:is_equivalent_to_tag_code ?object .
     FILTER NOT EXISTS { ?TWONTO owl:deprecated "true"^^xsd:boolean }
 }</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#pulsation_dampener</t>
+  </si>
+  <si>
+    <t>PDM</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#crane</t>
+  </si>
+  <si>
+    <t>CRN</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#manhole</t>
+  </si>
+  <si>
+    <t>MH</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#disconnect_switch</t>
+  </si>
+  <si>
+    <t>DS</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#capacitor</t>
+  </si>
+  <si>
+    <t>CAP</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#level_sensor_element</t>
+  </si>
+  <si>
+    <t>LE</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#PA_speaker</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>AMP</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#first_aid_kit</t>
+  </si>
+  <si>
+    <t>FAK</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#alarm</t>
+  </si>
+  <si>
+    <t>ALR</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#power_harmonic_filter</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#temperature_sensor_element</t>
+  </si>
+  <si>
+    <t>TE</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#well</t>
+  </si>
+  <si>
+    <t>WEL</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#compactor</t>
+  </si>
+  <si>
+    <t>CMP</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#motor_starter</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#spill_kit</t>
+  </si>
+  <si>
+    <t>SPL</t>
   </si>
 </sst>
 </file>
@@ -883,8 +922,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}" name="Table1" displayName="Table1" ref="A2:B139" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B139" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}" name="Table1" displayName="Table1" ref="A2:B141" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B141" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{6954C25C-9295-466B-8916-09F7AE9B1E9C}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{C2EFA1BF-9094-4221-B7A9-7713F0DEA95D}" name="Tag"/>
@@ -1190,7 +1229,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B139"/>
+  <dimension ref="A1:B141"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="56.7265625" bestFit="1" customWidth="1"/>
@@ -1199,7 +1238,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="174" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>241</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1212,831 +1251,831 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>101</v>
+        <v>193</v>
       </c>
       <c r="B5" t="s">
-        <v>3</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>102</v>
+        <v>222</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s">
-        <v>179</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>224</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>225</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>119</v>
+        <v>226</v>
       </c>
       <c r="B10" t="s">
-        <v>180</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>209</v>
+        <v>182</v>
       </c>
       <c r="B12" t="s">
-        <v>212</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>106</v>
+        <v>193</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>181</v>
+        <v>110</v>
       </c>
       <c r="B14" t="s">
-        <v>182</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B15" t="s">
-        <v>183</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="B16" t="s">
-        <v>184</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B19" t="s">
-        <v>186</v>
+        <v>84</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>98</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s">
-        <v>10</v>
+        <v>229</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>108</v>
+        <v>123</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="B22" t="s">
-        <v>188</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>209</v>
+        <v>130</v>
       </c>
       <c r="B24" t="s">
-        <v>211</v>
+        <v>32</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="B27" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>228</v>
+        <v>137</v>
       </c>
       <c r="B28" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="B30" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="B31" t="s">
-        <v>18</v>
+        <v>184</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>213</v>
+        <v>144</v>
       </c>
       <c r="B32" t="s">
-        <v>214</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="B33" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B34" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>117</v>
+        <v>189</v>
       </c>
       <c r="B35" t="s">
-        <v>84</v>
+        <v>190</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="B36" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>119</v>
+        <v>230</v>
       </c>
       <c r="B37" t="s">
-        <v>21</v>
+        <v>231</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="B38" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="B39" t="s">
-        <v>23</v>
+        <v>185</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>122</v>
+        <v>232</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>233</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>123</v>
+        <v>234</v>
       </c>
       <c r="B41" t="s">
-        <v>24</v>
+        <v>235</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>229</v>
+        <v>202</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>203</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>124</v>
+        <v>204</v>
       </c>
       <c r="B43" t="s">
-        <v>25</v>
+        <v>205</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>126</v>
+        <v>157</v>
       </c>
       <c r="B45" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>203</v>
+        <v>158</v>
       </c>
       <c r="B46" t="s">
-        <v>204</v>
+        <v>60</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>127</v>
+        <v>152</v>
       </c>
       <c r="B47" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>209</v>
+        <v>159</v>
       </c>
       <c r="B48" t="s">
-        <v>210</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="B49" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>129</v>
+        <v>164</v>
       </c>
       <c r="B50" t="s">
-        <v>31</v>
+        <v>65</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="B51" t="s">
-        <v>32</v>
+        <v>186</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>122</v>
+        <v>166</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>67</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>230</v>
+        <v>167</v>
       </c>
       <c r="B53" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B55" t="s">
-        <v>190</v>
+        <v>94</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>132</v>
+        <v>236</v>
       </c>
       <c r="B56" t="s">
-        <v>34</v>
+        <v>237</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>133</v>
+        <v>218</v>
       </c>
       <c r="B57" t="s">
-        <v>35</v>
+        <v>219</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="B58" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="B59" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>136</v>
+        <v>173</v>
       </c>
       <c r="B60" t="s">
-        <v>38</v>
+        <v>77</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>137</v>
+        <v>220</v>
       </c>
       <c r="B61" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>138</v>
+        <v>236</v>
       </c>
       <c r="B62" t="s">
-        <v>40</v>
+        <v>238</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>139</v>
+        <v>239</v>
       </c>
       <c r="B63" t="s">
-        <v>41</v>
+        <v>240</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="B64" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>141</v>
+        <v>176</v>
       </c>
       <c r="B65" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>125</v>
+        <v>177</v>
       </c>
       <c r="B66" t="s">
-        <v>191</v>
+        <v>81</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>142</v>
+        <v>178</v>
       </c>
       <c r="B67" t="s">
-        <v>44</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>226</v>
+        <v>99</v>
       </c>
       <c r="B68" t="s">
-        <v>227</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>143</v>
+        <v>101</v>
       </c>
       <c r="B69" t="s">
-        <v>45</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="B70" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="B71" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>189</v>
+        <v>105</v>
       </c>
       <c r="B72" t="s">
-        <v>96</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>192</v>
+        <v>106</v>
       </c>
       <c r="B73" t="s">
-        <v>193</v>
+        <v>8</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="B74" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>217</v>
+        <v>108</v>
       </c>
       <c r="B75" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>146</v>
+        <v>180</v>
       </c>
       <c r="B76" t="s">
-        <v>48</v>
+        <v>181</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>147</v>
+        <v>241</v>
       </c>
       <c r="B77" t="s">
-        <v>49</v>
+        <v>242</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B78" t="s">
-        <v>202</v>
+        <v>53</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="B79" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
       <c r="B80" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>150</v>
+        <v>115</v>
       </c>
       <c r="B81" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>151</v>
+        <v>118</v>
       </c>
       <c r="B82" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>152</v>
+        <v>119</v>
       </c>
       <c r="B83" t="s">
-        <v>87</v>
+        <v>21</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>218</v>
+        <v>120</v>
       </c>
       <c r="B84" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>231</v>
+        <v>121</v>
       </c>
       <c r="B85" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="B86" t="s">
-        <v>194</v>
+        <v>88</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>153</v>
+        <v>124</v>
       </c>
       <c r="B87" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>192</v>
+        <v>125</v>
       </c>
       <c r="B88" t="s">
-        <v>195</v>
+        <v>26</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>218</v>
+        <v>126</v>
       </c>
       <c r="B89" t="s">
-        <v>219</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>232</v>
+        <v>191</v>
       </c>
       <c r="B90" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>220</v>
+        <v>127</v>
       </c>
       <c r="B91" t="s">
-        <v>221</v>
+        <v>29</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="B92" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>155</v>
+        <v>243</v>
       </c>
       <c r="B93" t="s">
-        <v>24</v>
+        <v>244</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="B94" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="B95" t="s">
-        <v>59</v>
+        <v>183</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>158</v>
+        <v>132</v>
       </c>
       <c r="B96" t="s">
-        <v>60</v>
+        <v>34</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>189</v>
+        <v>133</v>
       </c>
       <c r="B97" t="s">
-        <v>95</v>
+        <v>35</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="B98" t="s">
-        <v>89</v>
+        <v>12</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="B99" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="B100" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>222</v>
+        <v>139</v>
       </c>
       <c r="B101" t="s">
-        <v>223</v>
+        <v>41</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>199</v>
+        <v>140</v>
       </c>
       <c r="B102" t="s">
-        <v>200</v>
+        <v>42</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>160</v>
+        <v>142</v>
       </c>
       <c r="B103" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="B104" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="B105" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>163</v>
+        <v>201</v>
       </c>
       <c r="B106" t="s">
         <v>47</v>
@@ -2044,266 +2083,282 @@
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="B107" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="B108" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>187</v>
+        <v>148</v>
       </c>
       <c r="B109" t="s">
-        <v>196</v>
+        <v>50</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>166</v>
+        <v>149</v>
       </c>
       <c r="B110" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="B111" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="B112" t="s">
-        <v>69</v>
+        <v>97</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>103</v>
+        <v>213</v>
       </c>
       <c r="B113" t="s">
-        <v>85</v>
+        <v>55</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>181</v>
+        <v>247</v>
       </c>
       <c r="B114" t="s">
-        <v>197</v>
+        <v>248</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="B115" t="s">
-        <v>94</v>
+        <v>56</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="B116" t="s">
-        <v>72</v>
+        <v>200</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>181</v>
+        <v>249</v>
       </c>
       <c r="B117" t="s">
-        <v>198</v>
+        <v>250</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>236</v>
+        <v>154</v>
       </c>
       <c r="B118" t="s">
-        <v>237</v>
+        <v>58</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="B119" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>224</v>
+        <v>182</v>
       </c>
       <c r="B120" t="s">
-        <v>225</v>
+        <v>95</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>170</v>
+        <v>215</v>
       </c>
       <c r="B121" t="s">
-        <v>71</v>
+        <v>216</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>171</v>
+        <v>206</v>
       </c>
       <c r="B122" t="s">
-        <v>73</v>
+        <v>207</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>121</v>
+        <v>187</v>
       </c>
       <c r="B123" t="s">
-        <v>75</v>
+        <v>188</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="B124" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="B125" t="s">
-        <v>208</v>
+        <v>63</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="B126" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>238</v>
+        <v>165</v>
       </c>
       <c r="B127" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="B128" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>158</v>
+        <v>251</v>
       </c>
       <c r="B129" t="s">
-        <v>205</v>
+        <v>252</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>99</v>
+        <v>217</v>
       </c>
       <c r="B130" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>206</v>
+        <v>253</v>
       </c>
       <c r="B131" t="s">
-        <v>207</v>
+        <v>254</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>175</v>
+        <v>208</v>
       </c>
       <c r="B132" t="s">
-        <v>79</v>
+        <v>209</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="B133" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="B134" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B135" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B136" t="s">
-        <v>1</v>
+        <v>78</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>117</v>
+        <v>175</v>
       </c>
       <c r="B137" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>201</v>
+        <v>156</v>
       </c>
       <c r="B138" t="s">
-        <v>239</v>
+        <v>87</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>240</v>
+        <v>117</v>
       </c>
       <c r="B139" t="s">
-        <v>215</v>
+        <v>86</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>189</v>
+      </c>
+      <c r="B140" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>193</v>
+      </c>
+      <c r="B141" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_tag.xlsx
+++ b/Avantis Mapping/SPARQL_tag.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5DB0E92-83C4-401E-BF2A-42FEC5D009D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6A0000-5372-4D99-9E8C-C7D433CBE3FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="248">
   <si>
     <t>TWONTO</t>
   </si>
@@ -332,294 +332,15 @@
     <t>FN</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#AC_evaporator_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_sensor_element</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#chlorinator_system</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#ozone_generator</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#gearbox</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pressure_transmitter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#clarifier</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pressurized_sewer_segment</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#channel_gate</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#security_camera</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#dehumidifier</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#engine</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#pipe_segment</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#chiller</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#centrifuge</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_handler_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#auto_sampler</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#automatic_external_defibrillator</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#operator_interface_terminal</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#valve</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#elevator</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#level_switch</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#power_washer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#display_panel</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#level_transmitter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#roll_up_door</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#UV_disinfection_assembly</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_gauge_or_display</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#transformer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#fixed_gas_detector</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#strainer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_scrubber</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#grinder_or_comminutor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_condition</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#heat_exchanger</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#computer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#AC_condenser_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#instrument_transmitter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#ejector</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#condensate_trap</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#classifier</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#flame_arrestor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#outfall_or_discharge_point</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_duct_segment</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#hydrant</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#dust_collector</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#fire_rated_door</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#screen</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#mixer_or_agitator</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#UPS</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#furnace</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#reservoir_tank</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#variable_air_volume_unit</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#flow_switch</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#flowmeter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#collector_mechanism</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#material_distribution_panel</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#controlled_door_access</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#flow_transmitter</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#server_appliance</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#motor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#quencher</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#transfer_switch</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#reactor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#trap_priming_device</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#battery</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#ash_lagoon</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#storage_tank</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#vibration_analyzer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#compressor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#air_damper</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#boiler</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#conveyor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#hydraulic_power_pack</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#surge_suppressor</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#backflow_preventer</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#annunciator_panel</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#ladder</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#data_logger</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#ground_and_test_device</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#humidifier</t>
-  </si>
-  <si>
-    <t>LI</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#temperature_transmitter</t>
-  </si>
-  <si>
-    <t>TIT</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#position_sensing</t>
-  </si>
-  <si>
-    <t>PI</t>
-  </si>
-  <si>
-    <t>TI</t>
-  </si>
-  <si>
-    <t>FQ</t>
-  </si>
-  <si>
-    <t>TT</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#process_control_panel</t>
-  </si>
-  <si>
     <t>CP</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#RPU_panel</t>
-  </si>
-  <si>
     <t>RPU</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#cable_segment</t>
-  </si>
-  <si>
     <t>CBL</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#weight_scale</t>
-  </si>
-  <si>
     <t>WSC</t>
   </si>
   <si>
@@ -629,9 +350,6 @@
     <t>WRT</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#motion_sensor_element</t>
-  </si>
-  <si>
     <t>MS</t>
   </si>
   <si>
@@ -641,70 +359,25 @@
     <t>LP</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#battery_charger</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#blower</t>
-  </si>
-  <si>
     <t>BL</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#SCBA</t>
-  </si>
-  <si>
     <t>SCBA</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#protection_relay</t>
-  </si>
-  <si>
     <t>AFR</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#generator</t>
-  </si>
-  <si>
     <t>GEN</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#burner_-_component_of_asset</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#process_controller</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#flow_sensor_element</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#heater</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#lighting_panel</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#chemical_dosing_system</t>
-  </si>
-  <si>
     <t>FD</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#equipment_chamber_or_access_chamber</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#torque_switch</t>
-  </si>
-  <si>
     <t>XSH</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#stationary_tool</t>
-  </si>
-  <si>
     <t>RTU</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#sludge_density_meter</t>
   </si>
   <si>
     <t>PREFIX rdf: &lt;http://www.w3.org/1999/02/22-rdf-syntax-ns#&gt;
@@ -719,97 +392,403 @@
 }</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#pulsation_dampener</t>
-  </si>
-  <si>
     <t>PDM</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#crane</t>
-  </si>
-  <si>
     <t>CRN</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#manhole</t>
-  </si>
-  <si>
     <t>MH</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#disconnect_switch</t>
-  </si>
-  <si>
     <t>DS</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#capacitor</t>
-  </si>
-  <si>
     <t>CAP</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#level_sensor_element</t>
-  </si>
-  <si>
     <t>LE</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#PA_speaker</t>
-  </si>
-  <si>
     <t>PA</t>
   </si>
   <si>
     <t>AMP</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#first_aid_kit</t>
-  </si>
-  <si>
     <t>FAK</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#alarm</t>
-  </si>
-  <si>
     <t>ALR</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#power_harmonic_filter</t>
-  </si>
-  <si>
     <t>HF</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#temperature_sensor_element</t>
-  </si>
-  <si>
     <t>TE</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#well</t>
-  </si>
-  <si>
     <t>WEL</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#compactor</t>
-  </si>
-  <si>
     <t>CMP</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#motor_starter</t>
-  </si>
-  <si>
     <t>ST</t>
   </si>
   <si>
-    <t>http://www.toronto.ca/TWONTO#spill_kit</t>
-  </si>
-  <si>
     <t>SPL</t>
+  </si>
+  <si>
+    <t>burner - component of asset</t>
+  </si>
+  <si>
+    <t>storage tank</t>
+  </si>
+  <si>
+    <t>auto sampler</t>
+  </si>
+  <si>
+    <t>lighting panel</t>
+  </si>
+  <si>
+    <t>flow sensor element</t>
+  </si>
+  <si>
+    <t>generator</t>
+  </si>
+  <si>
+    <t>ground fault tester</t>
+  </si>
+  <si>
+    <t>ladder</t>
+  </si>
+  <si>
+    <t>collector mechanism</t>
+  </si>
+  <si>
+    <t>flowmeter</t>
+  </si>
+  <si>
+    <t>blower</t>
+  </si>
+  <si>
+    <t>humidifier</t>
+  </si>
+  <si>
+    <t>level sensor element</t>
+  </si>
+  <si>
+    <t>manhole</t>
+  </si>
+  <si>
+    <t>air condition</t>
+  </si>
+  <si>
+    <t>instrument sensor element</t>
+  </si>
+  <si>
+    <t>transfer switch</t>
+  </si>
+  <si>
+    <t>trap priming device</t>
+  </si>
+  <si>
+    <t>power washer</t>
+  </si>
+  <si>
+    <t>spill kit</t>
+  </si>
+  <si>
+    <t>position sensing</t>
+  </si>
+  <si>
+    <t>dehumidifier</t>
+  </si>
+  <si>
+    <t>temperature sensor element</t>
+  </si>
+  <si>
+    <t>security camera</t>
+  </si>
+  <si>
+    <t>dust collector</t>
+  </si>
+  <si>
+    <t>chlorinator system</t>
+  </si>
+  <si>
+    <t>air handler unit</t>
+  </si>
+  <si>
+    <t>instrument gauge or display</t>
+  </si>
+  <si>
+    <t>channel gate</t>
+  </si>
+  <si>
+    <t>compactor</t>
+  </si>
+  <si>
+    <t>quencher</t>
+  </si>
+  <si>
+    <t>pipe segment</t>
+  </si>
+  <si>
+    <t>hydraulic power pack</t>
+  </si>
+  <si>
+    <t>operator interface terminal</t>
+  </si>
+  <si>
+    <t>fire rated door</t>
+  </si>
+  <si>
+    <t>cable segment</t>
+  </si>
+  <si>
+    <t>level transmitter</t>
+  </si>
+  <si>
+    <t>roll up door</t>
+  </si>
+  <si>
+    <t>variable air volume unit</t>
+  </si>
+  <si>
+    <t>UV disinfection assembly</t>
+  </si>
+  <si>
+    <t>equipment chamber or access chamber</t>
+  </si>
+  <si>
+    <t>flow switch</t>
+  </si>
+  <si>
+    <t>controlled door access</t>
+  </si>
+  <si>
+    <t>grinder or comminutor</t>
+  </si>
+  <si>
+    <t>air scrubber</t>
+  </si>
+  <si>
+    <t>backflow preventer</t>
+  </si>
+  <si>
+    <t>condensate trap</t>
+  </si>
+  <si>
+    <t>pressure transmitter</t>
+  </si>
+  <si>
+    <t>chemical dosing system</t>
+  </si>
+  <si>
+    <t>evaporator</t>
+  </si>
+  <si>
+    <t>ozone generator</t>
+  </si>
+  <si>
+    <t>disconnect switch</t>
+  </si>
+  <si>
+    <t>RPU panel</t>
+  </si>
+  <si>
+    <t>elevator</t>
+  </si>
+  <si>
+    <t>valve</t>
+  </si>
+  <si>
+    <t>transformer</t>
+  </si>
+  <si>
+    <t>heat exchanger</t>
+  </si>
+  <si>
+    <t>strainer</t>
+  </si>
+  <si>
+    <t>flame arrestor</t>
+  </si>
+  <si>
+    <t>classifier</t>
+  </si>
+  <si>
+    <t>pulsation dampener</t>
+  </si>
+  <si>
+    <t>fixed gas detector</t>
+  </si>
+  <si>
+    <t>ejector</t>
+  </si>
+  <si>
+    <t>furnace</t>
+  </si>
+  <si>
+    <t>slude density meter</t>
+  </si>
+  <si>
+    <t>torque switch</t>
+  </si>
+  <si>
+    <t>display panel</t>
+  </si>
+  <si>
+    <t>air damper</t>
+  </si>
+  <si>
+    <t>heater</t>
+  </si>
+  <si>
+    <t>motor starter</t>
+  </si>
+  <si>
+    <t>battery</t>
+  </si>
+  <si>
+    <t>server appliance</t>
+  </si>
+  <si>
+    <t>boiler</t>
+  </si>
+  <si>
+    <t>material distribution panel</t>
+  </si>
+  <si>
+    <t>weight scale</t>
+  </si>
+  <si>
+    <t>PA speaker</t>
+  </si>
+  <si>
+    <t>power harmonic filter</t>
+  </si>
+  <si>
+    <t>vibration analyzer</t>
+  </si>
+  <si>
+    <t>capacitor</t>
+  </si>
+  <si>
+    <t>well</t>
+  </si>
+  <si>
+    <t>groundskeeping equipment</t>
+  </si>
+  <si>
+    <t>Grounds</t>
+  </si>
+  <si>
+    <t>process control panel</t>
+  </si>
+  <si>
+    <t>computer</t>
+  </si>
+  <si>
+    <t>centrifuge</t>
+  </si>
+  <si>
+    <t>screen</t>
+  </si>
+  <si>
+    <t>mixer or agitator</t>
+  </si>
+  <si>
+    <t>pressurized sewer segment</t>
+  </si>
+  <si>
+    <t>annunciator panel</t>
+  </si>
+  <si>
+    <t>first aid kit</t>
+  </si>
+  <si>
+    <t>gearbox</t>
+  </si>
+  <si>
+    <t>level switch</t>
+  </si>
+  <si>
+    <t>outfall or discharge point</t>
+  </si>
+  <si>
+    <t>stationary tool</t>
+  </si>
+  <si>
+    <t>air duct segment</t>
+  </si>
+  <si>
+    <t>chiller</t>
+  </si>
+  <si>
+    <t>alarm</t>
+  </si>
+  <si>
+    <t>motion sensor element</t>
+  </si>
+  <si>
+    <t>ash lagoon</t>
+  </si>
+  <si>
+    <t>data logger</t>
+  </si>
+  <si>
+    <t>process controller</t>
+  </si>
+  <si>
+    <t>automatic external defibrillator</t>
+  </si>
+  <si>
+    <t>motor</t>
+  </si>
+  <si>
+    <t>engine</t>
+  </si>
+  <si>
+    <t>conveyor</t>
+  </si>
+  <si>
+    <t>reactor</t>
+  </si>
+  <si>
+    <t>instrument transmitter</t>
+  </si>
+  <si>
+    <t>condenser</t>
+  </si>
+  <si>
+    <t>clarifier</t>
+  </si>
+  <si>
+    <t>crane</t>
+  </si>
+  <si>
+    <t>surge suppressor</t>
+  </si>
+  <si>
+    <t>compressor</t>
+  </si>
+  <si>
+    <t>reservoir tank</t>
+  </si>
+  <si>
+    <t>battery charger</t>
+  </si>
+  <si>
+    <t>flow transmitter</t>
+  </si>
+  <si>
+    <t>protection relay</t>
+  </si>
+  <si>
+    <t>hydrant</t>
   </si>
 </sst>
 </file>
@@ -922,8 +901,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}" name="Table1" displayName="Table1" ref="A2:B141" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B141" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}" name="Table1" displayName="Table1" ref="A2:B138" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B138" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{6954C25C-9295-466B-8916-09F7AE9B1E9C}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{C2EFA1BF-9094-4221-B7A9-7713F0DEA95D}" name="Tag"/>
@@ -1229,7 +1208,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B141"/>
+  <dimension ref="A1:B138"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="56.7265625" bestFit="1" customWidth="1"/>
@@ -1238,7 +1217,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="174" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>223</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1251,943 +1230,943 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>193</v>
+        <v>133</v>
       </c>
       <c r="B5" t="s">
-        <v>196</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>222</v>
+        <v>134</v>
       </c>
       <c r="B6" t="s">
-        <v>199</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="B7" t="s">
-        <v>179</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>224</v>
+        <v>137</v>
       </c>
       <c r="B9" t="s">
-        <v>225</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>226</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s">
-        <v>227</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>182</v>
+        <v>140</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>193</v>
+        <v>141</v>
       </c>
       <c r="B13" t="s">
-        <v>195</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>197</v>
+        <v>144</v>
       </c>
       <c r="B17" t="s">
-        <v>198</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="B19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>228</v>
+        <v>147</v>
       </c>
       <c r="B20" t="s">
-        <v>229</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>211</v>
+        <v>149</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s">
-        <v>32</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>212</v>
+        <v>152</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>126</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>135</v>
+        <v>154</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="B28" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="B31" t="s">
-        <v>184</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>128</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="B34" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
       <c r="B35" t="s">
-        <v>190</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="B36" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>230</v>
+        <v>164</v>
       </c>
       <c r="B37" t="s">
-        <v>231</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="B38" t="s">
-        <v>87</v>
+        <v>24</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>152</v>
+        <v>166</v>
       </c>
       <c r="B39" t="s">
-        <v>185</v>
+        <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>232</v>
+        <v>167</v>
       </c>
       <c r="B40" t="s">
-        <v>233</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>234</v>
+        <v>168</v>
       </c>
       <c r="B41" t="s">
-        <v>235</v>
+        <v>24</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>202</v>
+        <v>169</v>
       </c>
       <c r="B42" t="s">
-        <v>203</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>204</v>
+        <v>167</v>
       </c>
       <c r="B43" t="s">
-        <v>205</v>
+        <v>92</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="B44" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="B45" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="B46" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="B47" t="s">
-        <v>89</v>
+        <v>54</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="B48" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="B49" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B50" t="s">
-        <v>65</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B51" t="s">
-        <v>186</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="B52" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="B53" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>103</v>
+        <v>179</v>
       </c>
       <c r="B54" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>117</v>
+        <v>180</v>
       </c>
       <c r="B55" t="s">
-        <v>94</v>
+        <v>10</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>236</v>
+        <v>181</v>
       </c>
       <c r="B56" t="s">
-        <v>237</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>218</v>
+        <v>182</v>
       </c>
       <c r="B57" t="s">
-        <v>219</v>
+        <v>118</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="B58" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>121</v>
+        <v>184</v>
       </c>
       <c r="B59" t="s">
-        <v>75</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="B60" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>220</v>
+        <v>186</v>
       </c>
       <c r="B61" t="s">
-        <v>74</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>236</v>
+        <v>187</v>
       </c>
       <c r="B62" t="s">
-        <v>238</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="B63" t="s">
-        <v>240</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>99</v>
+        <v>189</v>
       </c>
       <c r="B64" t="s">
-        <v>82</v>
+        <v>41</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="B65" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="B66" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="B67" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>99</v>
+        <v>193</v>
       </c>
       <c r="B68" t="s">
-        <v>6</v>
+        <v>38</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>101</v>
+        <v>194</v>
       </c>
       <c r="B69" t="s">
-        <v>3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>102</v>
+        <v>195</v>
       </c>
       <c r="B70" t="s">
-        <v>4</v>
+        <v>105</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>103</v>
+        <v>196</v>
       </c>
       <c r="B71" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>105</v>
+        <v>197</v>
       </c>
       <c r="B72" t="s">
-        <v>7</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>106</v>
+        <v>198</v>
       </c>
       <c r="B73" t="s">
-        <v>8</v>
+        <v>69</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>98</v>
+        <v>199</v>
       </c>
       <c r="B74" t="s">
-        <v>10</v>
+        <v>55</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>108</v>
+        <v>178</v>
       </c>
       <c r="B75" t="s">
-        <v>11</v>
+        <v>90</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>180</v>
+        <v>49</v>
       </c>
       <c r="B76" t="s">
-        <v>181</v>
+        <v>49</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>241</v>
+        <v>200</v>
       </c>
       <c r="B77" t="s">
-        <v>242</v>
+        <v>129</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="B78" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>112</v>
+        <v>202</v>
       </c>
       <c r="B79" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>114</v>
+        <v>203</v>
       </c>
       <c r="B80" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>115</v>
+        <v>204</v>
       </c>
       <c r="B81" t="s">
-        <v>19</v>
+        <v>58</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>118</v>
+        <v>205</v>
       </c>
       <c r="B82" t="s">
-        <v>20</v>
+        <v>102</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>119</v>
+        <v>206</v>
       </c>
       <c r="B83" t="s">
-        <v>21</v>
+        <v>121</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>120</v>
+        <v>207</v>
       </c>
       <c r="B84" t="s">
-        <v>22</v>
+        <v>125</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>121</v>
+        <v>208</v>
       </c>
       <c r="B85" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>122</v>
+        <v>209</v>
       </c>
       <c r="B86" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>124</v>
+        <v>210</v>
       </c>
       <c r="B87" t="s">
-        <v>25</v>
+        <v>127</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>125</v>
+        <v>211</v>
       </c>
       <c r="B88" t="s">
-        <v>26</v>
+        <v>212</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>126</v>
+        <v>213</v>
       </c>
       <c r="B89" t="s">
-        <v>27</v>
+        <v>98</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="B90" t="s">
-        <v>192</v>
+        <v>35</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>127</v>
+        <v>197</v>
       </c>
       <c r="B91" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B92" t="s">
-        <v>30</v>
+        <v>107</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>243</v>
+        <v>151</v>
       </c>
       <c r="B93" t="s">
-        <v>244</v>
+        <v>93</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>122</v>
+        <v>215</v>
       </c>
       <c r="B94" t="s">
-        <v>92</v>
+        <v>16</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>125</v>
+        <v>216</v>
       </c>
       <c r="B95" t="s">
-        <v>183</v>
+        <v>46</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>132</v>
+        <v>217</v>
       </c>
       <c r="B96" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>133</v>
+        <v>218</v>
       </c>
       <c r="B97" t="s">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>134</v>
+        <v>219</v>
       </c>
       <c r="B98" t="s">
-        <v>12</v>
+        <v>78</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>245</v>
+        <v>220</v>
       </c>
       <c r="B99" t="s">
-        <v>246</v>
+        <v>123</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>136</v>
+        <v>221</v>
       </c>
       <c r="B100" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="B101" t="s">
-        <v>41</v>
+        <v>108</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>140</v>
+        <v>222</v>
       </c>
       <c r="B102" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>142</v>
+        <v>223</v>
       </c>
       <c r="B103" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>143</v>
+        <v>224</v>
       </c>
       <c r="B104" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>182</v>
+        <v>225</v>
       </c>
       <c r="B105" t="s">
-        <v>96</v>
+        <v>43</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>201</v>
+        <v>167</v>
       </c>
       <c r="B106" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>146</v>
+        <v>226</v>
       </c>
       <c r="B107" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>147</v>
+        <v>227</v>
       </c>
       <c r="B108" t="s">
-        <v>49</v>
+        <v>124</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>148</v>
+        <v>228</v>
       </c>
       <c r="B109" t="s">
-        <v>50</v>
+        <v>104</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>149</v>
+        <v>229</v>
       </c>
       <c r="B110" t="s">
-        <v>51</v>
+        <v>65</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>151</v>
+        <v>230</v>
       </c>
       <c r="B111" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>202</v>
+        <v>231</v>
       </c>
       <c r="B112" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>213</v>
+        <v>185</v>
       </c>
       <c r="B113" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="B114" t="s">
-        <v>248</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>153</v>
+        <v>233</v>
       </c>
       <c r="B115" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>214</v>
+        <v>233</v>
       </c>
       <c r="B116" t="s">
-        <v>200</v>
+        <v>60</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="B117" t="s">
-        <v>250</v>
+        <v>13</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>154</v>
+        <v>235</v>
       </c>
       <c r="B118" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>156</v>
+        <v>236</v>
       </c>
       <c r="B119" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="B120" t="s">
         <v>95</v>
@@ -2195,170 +2174,146 @@
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="B121" t="s">
-        <v>216</v>
+        <v>37</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>206</v>
+        <v>238</v>
       </c>
       <c r="B122" t="s">
-        <v>207</v>
+        <v>12</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>187</v>
+        <v>239</v>
       </c>
       <c r="B123" t="s">
-        <v>188</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>160</v>
+        <v>183</v>
       </c>
       <c r="B124" t="s">
-        <v>62</v>
+        <v>113</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>161</v>
+        <v>240</v>
       </c>
       <c r="B125" t="s">
-        <v>63</v>
+        <v>116</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>163</v>
+        <v>241</v>
       </c>
       <c r="B126" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>165</v>
+        <v>242</v>
       </c>
       <c r="B127" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>168</v>
+        <v>205</v>
       </c>
       <c r="B128" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="B129" t="s">
-        <v>252</v>
+        <v>51</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="B130" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="B131" t="s">
-        <v>254</v>
+        <v>87</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="B132" t="s">
-        <v>209</v>
+        <v>109</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>170</v>
+        <v>205</v>
       </c>
       <c r="B133" t="s">
-        <v>71</v>
+        <v>103</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>171</v>
+        <v>245</v>
       </c>
       <c r="B134" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>172</v>
+        <v>247</v>
       </c>
       <c r="B135" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>174</v>
+        <v>247</v>
       </c>
       <c r="B136" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>175</v>
+        <v>206</v>
       </c>
       <c r="B137" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>156</v>
+        <v>185</v>
       </c>
       <c r="B138" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A139" t="s">
-        <v>117</v>
-      </c>
-      <c r="B139" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A140" t="s">
-        <v>189</v>
-      </c>
-      <c r="B140" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A141" t="s">
-        <v>193</v>
-      </c>
-      <c r="B141" t="s">
-        <v>194</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_tag.xlsx
+++ b/Avantis Mapping/SPARQL_tag.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6A0000-5372-4D99-9E8C-C7D433CBE3FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F8601E-55D0-435D-B0DD-5F566D6AD407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="250">
   <si>
     <t>TWONTO</t>
   </si>
@@ -378,6 +378,411 @@
   </si>
   <si>
     <t>RTU</t>
+  </si>
+  <si>
+    <t>PDM</t>
+  </si>
+  <si>
+    <t>CRN</t>
+  </si>
+  <si>
+    <t>MH</t>
+  </si>
+  <si>
+    <t>DS</t>
+  </si>
+  <si>
+    <t>CAP</t>
+  </si>
+  <si>
+    <t>LE</t>
+  </si>
+  <si>
+    <t>PA</t>
+  </si>
+  <si>
+    <t>AMP</t>
+  </si>
+  <si>
+    <t>FAK</t>
+  </si>
+  <si>
+    <t>ALR</t>
+  </si>
+  <si>
+    <t>HF</t>
+  </si>
+  <si>
+    <t>TE</t>
+  </si>
+  <si>
+    <t>WEL</t>
+  </si>
+  <si>
+    <t>CMP</t>
+  </si>
+  <si>
+    <t>ST</t>
+  </si>
+  <si>
+    <t>SPL</t>
+  </si>
+  <si>
+    <t>Grounds</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00781</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00117</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00431</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00368</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00806</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00622</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00168</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00644</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00233</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00251</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00718</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00122</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00219</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00236</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00447</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00589</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00245</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00636</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00316</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00531</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00164</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00614</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00255</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00156</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00530</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00151</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00213</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00467</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00144</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00703</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00551</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00466</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00396</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00123</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00355</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00154</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00608</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00526</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00665</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00200</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00179</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00279</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00234</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00613</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00408</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00811</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00194</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00791</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00595</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00502</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00183</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00680</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00167</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00532</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00124</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00605</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00418</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00142</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00750</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00689</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00385</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00294</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00359</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00625</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00220</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00361</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00710</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00416</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00755</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00306</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00272</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00553</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00321</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00206</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00235</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00165</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00148</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00405</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00244</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00367</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00446</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00318</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00126</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00784</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00649</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00192</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00353</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00548</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00433</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00569</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00633</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00232</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00202</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00445</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00147</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00215</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00263</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00733</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00671</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00292</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00757</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00596</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00700</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00141</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00754</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00493</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00429</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00369</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00465</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00457</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00226</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00397</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00406</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00366</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00477</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00163</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00708</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00191</t>
   </si>
   <si>
     <t>PREFIX rdf: &lt;http://www.w3.org/1999/02/22-rdf-syntax-ns#&gt;
@@ -385,410 +790,11 @@
 PREFIX rdfs: &lt;http://www.w3.org/2000/01/rdf-schema#&gt;
 PREFIX xsd: &lt;http://www.w3.org/2001/XMLSchema#&gt;
 PREFIX tw: &lt;http://www.toronto.ca/TWONTO#&gt;
-SELECT ?TWONTO (STR(?object) as ?Avantis)
+SELECT (STR(?sub) AS ?TWONTO) (STR(?object) AS ?Avantis)
 WHERE { 
-    ?TWONTO tw:is_equivalent_to_tag_code ?object .
-    FILTER NOT EXISTS { ?TWONTO owl:deprecated "true"^^xsd:boolean }
+    ?sub tw:is_equivalent_to_tag_code ?object .
+    FILTER NOT EXISTS { ?sub owl:deprecated "true"^^xsd:boolean }
 }</t>
-  </si>
-  <si>
-    <t>PDM</t>
-  </si>
-  <si>
-    <t>CRN</t>
-  </si>
-  <si>
-    <t>MH</t>
-  </si>
-  <si>
-    <t>DS</t>
-  </si>
-  <si>
-    <t>CAP</t>
-  </si>
-  <si>
-    <t>LE</t>
-  </si>
-  <si>
-    <t>PA</t>
-  </si>
-  <si>
-    <t>AMP</t>
-  </si>
-  <si>
-    <t>FAK</t>
-  </si>
-  <si>
-    <t>ALR</t>
-  </si>
-  <si>
-    <t>HF</t>
-  </si>
-  <si>
-    <t>TE</t>
-  </si>
-  <si>
-    <t>WEL</t>
-  </si>
-  <si>
-    <t>CMP</t>
-  </si>
-  <si>
-    <t>ST</t>
-  </si>
-  <si>
-    <t>SPL</t>
-  </si>
-  <si>
-    <t>burner - component of asset</t>
-  </si>
-  <si>
-    <t>storage tank</t>
-  </si>
-  <si>
-    <t>auto sampler</t>
-  </si>
-  <si>
-    <t>lighting panel</t>
-  </si>
-  <si>
-    <t>flow sensor element</t>
-  </si>
-  <si>
-    <t>generator</t>
-  </si>
-  <si>
-    <t>ground fault tester</t>
-  </si>
-  <si>
-    <t>ladder</t>
-  </si>
-  <si>
-    <t>collector mechanism</t>
-  </si>
-  <si>
-    <t>flowmeter</t>
-  </si>
-  <si>
-    <t>blower</t>
-  </si>
-  <si>
-    <t>humidifier</t>
-  </si>
-  <si>
-    <t>level sensor element</t>
-  </si>
-  <si>
-    <t>manhole</t>
-  </si>
-  <si>
-    <t>air condition</t>
-  </si>
-  <si>
-    <t>instrument sensor element</t>
-  </si>
-  <si>
-    <t>transfer switch</t>
-  </si>
-  <si>
-    <t>trap priming device</t>
-  </si>
-  <si>
-    <t>power washer</t>
-  </si>
-  <si>
-    <t>spill kit</t>
-  </si>
-  <si>
-    <t>position sensing</t>
-  </si>
-  <si>
-    <t>dehumidifier</t>
-  </si>
-  <si>
-    <t>temperature sensor element</t>
-  </si>
-  <si>
-    <t>security camera</t>
-  </si>
-  <si>
-    <t>dust collector</t>
-  </si>
-  <si>
-    <t>chlorinator system</t>
-  </si>
-  <si>
-    <t>air handler unit</t>
-  </si>
-  <si>
-    <t>instrument gauge or display</t>
-  </si>
-  <si>
-    <t>channel gate</t>
-  </si>
-  <si>
-    <t>compactor</t>
-  </si>
-  <si>
-    <t>quencher</t>
-  </si>
-  <si>
-    <t>pipe segment</t>
-  </si>
-  <si>
-    <t>hydraulic power pack</t>
-  </si>
-  <si>
-    <t>operator interface terminal</t>
-  </si>
-  <si>
-    <t>fire rated door</t>
-  </si>
-  <si>
-    <t>cable segment</t>
-  </si>
-  <si>
-    <t>level transmitter</t>
-  </si>
-  <si>
-    <t>roll up door</t>
-  </si>
-  <si>
-    <t>variable air volume unit</t>
-  </si>
-  <si>
-    <t>UV disinfection assembly</t>
-  </si>
-  <si>
-    <t>equipment chamber or access chamber</t>
-  </si>
-  <si>
-    <t>flow switch</t>
-  </si>
-  <si>
-    <t>controlled door access</t>
-  </si>
-  <si>
-    <t>grinder or comminutor</t>
-  </si>
-  <si>
-    <t>air scrubber</t>
-  </si>
-  <si>
-    <t>backflow preventer</t>
-  </si>
-  <si>
-    <t>condensate trap</t>
-  </si>
-  <si>
-    <t>pressure transmitter</t>
-  </si>
-  <si>
-    <t>chemical dosing system</t>
-  </si>
-  <si>
-    <t>evaporator</t>
-  </si>
-  <si>
-    <t>ozone generator</t>
-  </si>
-  <si>
-    <t>disconnect switch</t>
-  </si>
-  <si>
-    <t>RPU panel</t>
-  </si>
-  <si>
-    <t>elevator</t>
-  </si>
-  <si>
-    <t>valve</t>
-  </si>
-  <si>
-    <t>transformer</t>
-  </si>
-  <si>
-    <t>heat exchanger</t>
-  </si>
-  <si>
-    <t>strainer</t>
-  </si>
-  <si>
-    <t>flame arrestor</t>
-  </si>
-  <si>
-    <t>classifier</t>
-  </si>
-  <si>
-    <t>pulsation dampener</t>
-  </si>
-  <si>
-    <t>fixed gas detector</t>
-  </si>
-  <si>
-    <t>ejector</t>
-  </si>
-  <si>
-    <t>furnace</t>
-  </si>
-  <si>
-    <t>slude density meter</t>
-  </si>
-  <si>
-    <t>torque switch</t>
-  </si>
-  <si>
-    <t>display panel</t>
-  </si>
-  <si>
-    <t>air damper</t>
-  </si>
-  <si>
-    <t>heater</t>
-  </si>
-  <si>
-    <t>motor starter</t>
-  </si>
-  <si>
-    <t>battery</t>
-  </si>
-  <si>
-    <t>server appliance</t>
-  </si>
-  <si>
-    <t>boiler</t>
-  </si>
-  <si>
-    <t>material distribution panel</t>
-  </si>
-  <si>
-    <t>weight scale</t>
-  </si>
-  <si>
-    <t>PA speaker</t>
-  </si>
-  <si>
-    <t>power harmonic filter</t>
-  </si>
-  <si>
-    <t>vibration analyzer</t>
-  </si>
-  <si>
-    <t>capacitor</t>
-  </si>
-  <si>
-    <t>well</t>
-  </si>
-  <si>
-    <t>groundskeeping equipment</t>
-  </si>
-  <si>
-    <t>Grounds</t>
-  </si>
-  <si>
-    <t>process control panel</t>
-  </si>
-  <si>
-    <t>computer</t>
-  </si>
-  <si>
-    <t>centrifuge</t>
-  </si>
-  <si>
-    <t>screen</t>
-  </si>
-  <si>
-    <t>mixer or agitator</t>
-  </si>
-  <si>
-    <t>pressurized sewer segment</t>
-  </si>
-  <si>
-    <t>annunciator panel</t>
-  </si>
-  <si>
-    <t>first aid kit</t>
-  </si>
-  <si>
-    <t>gearbox</t>
-  </si>
-  <si>
-    <t>level switch</t>
-  </si>
-  <si>
-    <t>outfall or discharge point</t>
-  </si>
-  <si>
-    <t>stationary tool</t>
-  </si>
-  <si>
-    <t>air duct segment</t>
-  </si>
-  <si>
-    <t>chiller</t>
-  </si>
-  <si>
-    <t>alarm</t>
-  </si>
-  <si>
-    <t>motion sensor element</t>
-  </si>
-  <si>
-    <t>ash lagoon</t>
-  </si>
-  <si>
-    <t>data logger</t>
-  </si>
-  <si>
-    <t>process controller</t>
-  </si>
-  <si>
-    <t>automatic external defibrillator</t>
-  </si>
-  <si>
-    <t>motor</t>
-  </si>
-  <si>
-    <t>engine</t>
-  </si>
-  <si>
-    <t>conveyor</t>
-  </si>
-  <si>
-    <t>reactor</t>
-  </si>
-  <si>
-    <t>instrument transmitter</t>
-  </si>
-  <si>
-    <t>condenser</t>
-  </si>
-  <si>
-    <t>clarifier</t>
-  </si>
-  <si>
-    <t>crane</t>
-  </si>
-  <si>
-    <t>surge suppressor</t>
-  </si>
-  <si>
-    <t>compressor</t>
-  </si>
-  <si>
-    <t>reservoir tank</t>
-  </si>
-  <si>
-    <t>battery charger</t>
-  </si>
-  <si>
-    <t>flow transmitter</t>
-  </si>
-  <si>
-    <t>protection relay</t>
-  </si>
-  <si>
-    <t>hydrant</t>
   </si>
 </sst>
 </file>
@@ -901,8 +907,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}" name="Table1" displayName="Table1" ref="A2:B138" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B138" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}" name="Table1" displayName="Table1" ref="A2:B136" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B136" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{6954C25C-9295-466B-8916-09F7AE9B1E9C}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{C2EFA1BF-9094-4221-B7A9-7713F0DEA95D}" name="Tag"/>
@@ -1208,16 +1214,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B138"/>
+  <dimension ref="A1:B136"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="56.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="61.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="174" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>114</v>
+        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1233,7 +1239,7 @@
         <v>131</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>53</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -1241,7 +1247,7 @@
         <v>132</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1249,7 +1255,7 @@
         <v>133</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -1257,7 +1263,7 @@
         <v>134</v>
       </c>
       <c r="B6" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -1265,7 +1271,7 @@
         <v>135</v>
       </c>
       <c r="B7" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -1273,303 +1279,303 @@
         <v>136</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B14" t="s">
-        <v>1</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B16" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B21" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B23" t="s">
-        <v>130</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B24" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>153</v>
+        <v>131</v>
       </c>
       <c r="B26" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B27" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B29" t="s">
-        <v>2</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B30" t="s">
-        <v>17</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B31" t="s">
-        <v>26</v>
+        <v>123</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B32" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B33" t="s">
-        <v>128</v>
+        <v>91</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B34" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B35" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B37" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B39" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B40" t="s">
-        <v>88</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B41" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>48</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B44" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B45" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
@@ -1577,711 +1583,711 @@
         <v>146</v>
       </c>
       <c r="B46" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B47" t="s">
-        <v>54</v>
+        <v>107</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B48" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B49" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B50" t="s">
-        <v>31</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B51" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B52" t="s">
-        <v>39</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B53" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B54" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B55" t="s">
-        <v>10</v>
+        <v>124</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>181</v>
+        <v>132</v>
       </c>
       <c r="B56" t="s">
-        <v>3</v>
+        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>182</v>
+        <v>135</v>
       </c>
       <c r="B57" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B58" t="s">
-        <v>99</v>
+        <v>58</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B59" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B60" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B61" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B62" t="s">
-        <v>34</v>
+        <v>128</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B63" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B64" t="s">
-        <v>41</v>
+        <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B65" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B66" t="s">
-        <v>115</v>
+        <v>69</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="B67" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B68" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="B69" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B70" t="s">
-        <v>105</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B71" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B72" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B73" t="s">
-        <v>69</v>
+        <v>114</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B74" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="B75" t="s">
-        <v>90</v>
+        <v>41</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>49</v>
+        <v>197</v>
       </c>
       <c r="B76" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B77" t="s">
-        <v>129</v>
+        <v>34</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B78" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>202</v>
+        <v>131</v>
       </c>
       <c r="B79" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B80" t="s">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>204</v>
+        <v>142</v>
       </c>
       <c r="B81" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B82" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B83" t="s">
-        <v>121</v>
+        <v>3</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B84" t="s">
-        <v>125</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B85" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="B86" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B87" t="s">
-        <v>127</v>
+        <v>39</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B88" t="s">
-        <v>212</v>
+        <v>77</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B89" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="B90" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B91" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>141</v>
+        <v>210</v>
       </c>
       <c r="B92" t="s">
-        <v>107</v>
+        <v>54</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>151</v>
+        <v>211</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>6</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B94" t="s">
-        <v>16</v>
+        <v>72</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B95" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>217</v>
+        <v>158</v>
       </c>
       <c r="B96" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B97" t="s">
-        <v>7</v>
+        <v>52</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="B98" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>220</v>
+        <v>158</v>
       </c>
       <c r="B99" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="B100" t="s">
-        <v>4</v>
+        <v>100</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>108</v>
+        <v>217</v>
       </c>
       <c r="B101" t="s">
-        <v>108</v>
+        <v>24</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B102" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B103" t="s">
-        <v>42</v>
+        <v>73</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B104" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B105" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>167</v>
+        <v>222</v>
       </c>
       <c r="B106" t="s">
-        <v>91</v>
+        <v>127</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B107" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B108" t="s">
-        <v>124</v>
+        <v>26</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B109" t="s">
-        <v>104</v>
+        <v>17</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B110" t="s">
-        <v>65</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>230</v>
+        <v>146</v>
       </c>
       <c r="B111" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B112" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>185</v>
+        <v>228</v>
       </c>
       <c r="B113" t="s">
-        <v>84</v>
+        <v>125</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B114" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B115" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B116" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B117" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B118" t="s">
-        <v>71</v>
+        <v>129</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B119" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>151</v>
+        <v>211</v>
       </c>
       <c r="B120" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B121" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B122" t="s">
-        <v>12</v>
+        <v>116</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B123" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>183</v>
+        <v>238</v>
       </c>
       <c r="B124" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B125" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="B126" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B127" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="B128" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B129" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B130" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B131" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B132" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>205</v>
+        <v>245</v>
       </c>
       <c r="B133" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B134" t="s">
-        <v>89</v>
+        <v>18</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
@@ -2289,31 +2295,15 @@
         <v>247</v>
       </c>
       <c r="B135" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B136" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A137" t="s">
-        <v>206</v>
-      </c>
-      <c r="B137" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A138" t="s">
-        <v>185</v>
-      </c>
-      <c r="B138" t="s">
-        <v>94</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/Avantis Mapping/SPARQL_tag.xlsx
+++ b/Avantis Mapping/SPARQL_tag.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\medney\Documents\GitHub\TWONTO\Avantis Mapping\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F8601E-55D0-435D-B0DD-5F566D6AD407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EBDD5FC-2227-4AAC-A1E1-06F5F882707C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{716C0CF8-2E33-46F2-BE6F-578AC5702A19}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="299">
   <si>
     <t>TWONTO</t>
   </si>
@@ -218,9 +218,6 @@
     <t>SERV</t>
   </si>
   <si>
-    <t>m</t>
-  </si>
-  <si>
     <t>QUEN</t>
   </si>
   <si>
@@ -675,9 +672,6 @@
   </si>
   <si>
     <t>http://www.toronto.ca/TWONTO#00318</t>
-  </si>
-  <si>
-    <t>http://www.toronto.ca/TWONTO#00126</t>
   </si>
   <si>
     <t>http://www.toronto.ca/TWONTO#00784</t>
@@ -795,6 +789,159 @@
     ?sub tw:is_equivalent_to_tag_code ?object .
     FILTER NOT EXISTS { ?sub owl:deprecated "true"^^xsd:boolean }
 }</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00288</t>
+  </si>
+  <si>
+    <t>DRN</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00761</t>
+  </si>
+  <si>
+    <t>LOA</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00520</t>
+  </si>
+  <si>
+    <t>INQ</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00933</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00568</t>
+  </si>
+  <si>
+    <t>MAN</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00922</t>
+  </si>
+  <si>
+    <t>IGN</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00626</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00702</t>
+  </si>
+  <si>
+    <t>TEL</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00932</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00918</t>
+  </si>
+  <si>
+    <t>NGR</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00655</t>
+  </si>
+  <si>
+    <t>RD</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00814</t>
+  </si>
+  <si>
+    <t>WAP</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00668</t>
+  </si>
+  <si>
+    <t>SCP</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00563</t>
+  </si>
+  <si>
+    <t>SS</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00716</t>
+  </si>
+  <si>
+    <t>SO</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00923</t>
+  </si>
+  <si>
+    <t>LHD</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00105</t>
+  </si>
+  <si>
+    <t>PSU</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00921</t>
+  </si>
+  <si>
+    <t>FSP</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00362</t>
+  </si>
+  <si>
+    <t>FDT</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00915</t>
+  </si>
+  <si>
+    <t>FEQ</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00805</t>
+  </si>
+  <si>
+    <t>WS</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00925</t>
+  </si>
+  <si>
+    <t>BN</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00558</t>
+  </si>
+  <si>
+    <t>STRC</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00474</t>
+  </si>
+  <si>
+    <t>LD</t>
+  </si>
+  <si>
+    <t>http://www.toronto.ca/TWONTO#00657</t>
+  </si>
+  <si>
+    <t>SQ</t>
   </si>
 </sst>
 </file>
@@ -907,8 +1054,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}" name="Table1" displayName="Table1" ref="A2:B136" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A2:B136" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}" name="Table1" displayName="Table1" ref="A2:B161" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A2:B161" xr:uid="{3BC09C4A-7B59-4975-AFA2-25A1F79AB441}"/>
   <tableColumns count="2">
     <tableColumn id="1" xr3:uid="{6954C25C-9295-466B-8916-09F7AE9B1E9C}" name="TWONTO"/>
     <tableColumn id="2" xr3:uid="{C2EFA1BF-9094-4221-B7A9-7713F0DEA95D}" name="Tag"/>
@@ -1214,7 +1361,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C799550E-49B1-4512-9CC1-86876BA1337E}">
-  <dimension ref="A1:B136"/>
+  <dimension ref="A1:B161"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="56.7265625" bestFit="1" customWidth="1"/>
@@ -1223,7 +1370,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1231,55 +1378,55 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>131</v>
+        <v>248</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>94</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B7" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>136</v>
+        <v>250</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>251</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -1287,1022 +1434,1222 @@
         <v>134</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>138</v>
+        <v>252</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B13" t="s">
-        <v>101</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>140</v>
+        <v>254</v>
       </c>
       <c r="B14" t="s">
-        <v>115</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>141</v>
+        <v>255</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>256</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B16" t="s">
-        <v>113</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>143</v>
+        <v>258</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
+        <v>259</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="B19" t="s">
-        <v>37</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="B20" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>147</v>
+        <v>260</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>261</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="B23" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="B26" t="s">
-        <v>84</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="B28" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="B31" t="s">
-        <v>123</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>158</v>
+        <v>130</v>
       </c>
       <c r="B33" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="B35" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>161</v>
+        <v>262</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>263</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="B37" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="B38" t="s">
-        <v>4</v>
+        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="B39" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
       <c r="B40" t="s">
-        <v>122</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="B41" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="B42" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="B43" t="s">
-        <v>48</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>169</v>
+        <v>264</v>
       </c>
       <c r="B44" t="s">
-        <v>46</v>
+        <v>265</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B45" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="B47" t="s">
-        <v>107</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="B48" t="s">
-        <v>23</v>
+        <v>107</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="B49" t="s">
-        <v>35</v>
+        <v>121</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="B50" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>175</v>
+        <v>266</v>
       </c>
       <c r="B51" t="s">
-        <v>130</v>
+        <v>267</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B52" t="s">
-        <v>126</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B53" t="s">
-        <v>118</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B54" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="B55" t="s">
-        <v>124</v>
+        <v>16</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="B56" t="s">
-        <v>120</v>
+        <v>92</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="B57" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="B59" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B60" t="s">
-        <v>59</v>
+        <v>97</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="B61" t="s">
-        <v>47</v>
+        <v>129</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="B62" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="B63" t="s">
-        <v>49</v>
+        <v>117</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="B64" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="B65" t="s">
-        <v>55</v>
+        <v>123</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>188</v>
+        <v>131</v>
       </c>
       <c r="B66" t="s">
-        <v>69</v>
+        <v>119</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>172</v>
+        <v>268</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>269</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>189</v>
+        <v>134</v>
       </c>
       <c r="B68" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="B69" t="s">
-        <v>105</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="B70" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="B71" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="B72" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="B73" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="B74" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>196</v>
+        <v>270</v>
       </c>
       <c r="B75" t="s">
-        <v>41</v>
+        <v>271</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="B76" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="B77" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="B78" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="B79" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="B80" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="B81" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="B82" t="s">
-        <v>117</v>
+        <v>50</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="B83" t="s">
-        <v>3</v>
+        <v>38</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="B84" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="B85" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B86" t="s">
-        <v>85</v>
+        <v>40</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="B87" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="B88" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="B89" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="B90" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>209</v>
+        <v>159</v>
       </c>
       <c r="B91" t="s">
-        <v>24</v>
+        <v>272</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>210</v>
+        <v>130</v>
       </c>
       <c r="B92" t="s">
-        <v>54</v>
+        <v>85</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="B93" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>212</v>
+        <v>141</v>
       </c>
       <c r="B94" t="s">
-        <v>72</v>
+        <v>98</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>213</v>
+        <v>273</v>
       </c>
       <c r="B95" t="s">
-        <v>25</v>
+        <v>274</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>158</v>
+        <v>200</v>
       </c>
       <c r="B96" t="s">
-        <v>92</v>
+        <v>116</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="B97" t="s">
-        <v>52</v>
+        <v>3</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="B98" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>158</v>
+        <v>203</v>
       </c>
       <c r="B99" t="s">
-        <v>88</v>
+        <v>110</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
-        <v>216</v>
+        <v>275</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>276</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="B101" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>218</v>
+        <v>277</v>
       </c>
       <c r="B102" t="s">
-        <v>36</v>
+        <v>278</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="B103" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="B104" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="B105" t="s">
-        <v>61</v>
+        <v>31</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="B106" t="s">
-        <v>127</v>
+        <v>32</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="B107" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="B108" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="B109" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>226</v>
+        <v>279</v>
       </c>
       <c r="B110" t="s">
-        <v>2</v>
+        <v>280</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>146</v>
+        <v>211</v>
       </c>
       <c r="B111" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>227</v>
+        <v>157</v>
       </c>
       <c r="B112" t="s">
-        <v>11</v>
+        <v>91</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="B113" t="s">
-        <v>125</v>
+        <v>52</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
       <c r="B114" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>230</v>
+        <v>157</v>
       </c>
       <c r="B115" t="s">
-        <v>45</v>
+        <v>87</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="B116" t="s">
-        <v>64</v>
+        <v>99</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="B117" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="B118" t="s">
-        <v>129</v>
+        <v>36</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="B119" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>211</v>
+        <v>281</v>
       </c>
       <c r="B120" t="s">
-        <v>82</v>
+        <v>282</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="B121" t="s">
-        <v>62</v>
+        <v>14</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="B122" t="s">
-        <v>116</v>
+        <v>60</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="B123" t="s">
-        <v>1</v>
+        <v>126</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>238</v>
+        <v>283</v>
       </c>
       <c r="B124" t="s">
-        <v>89</v>
+        <v>284</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>239</v>
+        <v>221</v>
       </c>
       <c r="B125" t="s">
-        <v>119</v>
+        <v>8</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>171</v>
+        <v>222</v>
       </c>
       <c r="B126" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="B127" t="s">
-        <v>79</v>
+        <v>17</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="B128" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>238</v>
+        <v>145</v>
       </c>
       <c r="B129" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="B130" t="s">
-        <v>110</v>
+        <v>11</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="B131" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>244</v>
+        <v>285</v>
       </c>
       <c r="B132" t="s">
-        <v>28</v>
+        <v>286</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>245</v>
+        <v>287</v>
       </c>
       <c r="B133" t="s">
-        <v>106</v>
+        <v>288</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="B134" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="B135" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="B136" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A137" t="s">
+        <v>230</v>
+      </c>
+      <c r="B137" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A138" t="s">
+        <v>231</v>
+      </c>
+      <c r="B138" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A139" t="s">
+        <v>289</v>
+      </c>
+      <c r="B139" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A140" t="s">
+        <v>232</v>
+      </c>
+      <c r="B140" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A141" t="s">
+        <v>210</v>
+      </c>
+      <c r="B141" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A142" t="s">
+        <v>291</v>
+      </c>
+      <c r="B142" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A143" t="s">
+        <v>233</v>
+      </c>
+      <c r="B143" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A144" t="s">
+        <v>234</v>
+      </c>
+      <c r="B144" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A145" t="s">
+        <v>235</v>
+      </c>
+      <c r="B145" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A146" t="s">
+        <v>236</v>
+      </c>
+      <c r="B146" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A147" t="s">
+        <v>237</v>
+      </c>
+      <c r="B147" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A148" t="s">
+        <v>293</v>
+      </c>
+      <c r="B148" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
+        <v>170</v>
+      </c>
+      <c r="B149" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A150" t="s">
+        <v>238</v>
+      </c>
+      <c r="B150" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A151" t="s">
+        <v>239</v>
+      </c>
+      <c r="B151" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A152" t="s">
+        <v>295</v>
+      </c>
+      <c r="B152" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A153" t="s">
+        <v>236</v>
+      </c>
+      <c r="B153" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A154" t="s">
+        <v>240</v>
+      </c>
+      <c r="B154" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A155" t="s">
+        <v>241</v>
+      </c>
+      <c r="B155" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A156" t="s">
+        <v>242</v>
+      </c>
+      <c r="B156" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A157" t="s">
+        <v>297</v>
+      </c>
+      <c r="B157" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A158" t="s">
+        <v>243</v>
+      </c>
+      <c r="B158" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A159" t="s">
+        <v>244</v>
+      </c>
+      <c r="B159" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A160" t="s">
+        <v>245</v>
+      </c>
+      <c r="B160" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A161" t="s">
+        <v>246</v>
+      </c>
+      <c r="B161" t="s">
         <v>53</v>
       </c>
     </row>
